--- a/EMPREENDEDORAS_PAM_VERDE_C3_2026.xlsx
+++ b/EMPREENDEDORAS_PAM_VERDE_C3_2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30327"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://muvamozorg.sharepoint.com/sites/mis.drive/Documentos Partilhados/PROJECTOS/Sistema de Monitoria/Pam_Verde/2026/Baseline_Endline/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="215" documentId="11_0DFBC18E49307CB38E73D6987E34D4946C7A7096" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{662CF095-CF90-40A3-9454-44CB2AA9DD0A}"/>
+  <xr:revisionPtr revIDLastSave="227" documentId="11_0DFBC18E49307CB38E73D6987E34D4946C7A7096" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A74B5B17-BBE3-4152-AAAE-83EBE1C8126C}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Empreendedoras_Nampula_C3_2026" sheetId="1" r:id="rId1"/>
@@ -3876,7 +3876,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd\-mmm\-yyyy"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -3965,8 +3965,8 @@
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{0909418B-F909-4D55-ABD8-6E07EE1D6696}" name="Table1" displayName="Table1" ref="A1:CJ51" totalsRowShown="0">
   <autoFilter ref="A1:CJ51" xr:uid="{0909418B-F909-4D55-ABD8-6E07EE1D6696}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:CJ51">
-    <sortCondition ref="F1:F51"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:CJ48">
+    <sortCondition ref="G1:G51"/>
   </sortState>
   <tableColumns count="88">
     <tableColumn id="1" xr3:uid="{CF58FB95-54F2-4F03-A38C-EFABEFE93F6E}" name="Confirma que compreendeu a informação acima e aceita participar nesta entrevista?"/>
@@ -4380,7 +4380,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:CL51"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="16" hidden="1" customWidth="1"/>
     <col min="4" max="4" width="11.7109375" hidden="1" customWidth="1"/>
@@ -4402,7 +4402,7 @@
     <col min="88" max="88" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:88">
+    <row r="1" spans="1:88" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -4668,7 +4668,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="2" spans="1:88">
+    <row r="2" spans="1:88" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>88</v>
       </c>
@@ -4934,7 +4934,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="3" spans="1:88">
+    <row r="3" spans="1:88" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>88</v>
       </c>
@@ -5197,7 +5197,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="4" spans="1:88">
+    <row r="4" spans="1:88" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>88</v>
       </c>
@@ -5460,7 +5460,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="5" spans="1:88">
+    <row r="5" spans="1:88" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>88</v>
       </c>
@@ -5724,7 +5724,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="6" spans="1:88">
+    <row r="6" spans="1:88" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>88</v>
       </c>
@@ -5987,7 +5987,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="7" spans="1:88">
+    <row r="7" spans="1:88" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>88</v>
       </c>
@@ -6250,7 +6250,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="8" spans="1:88">
+    <row r="8" spans="1:88" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>88</v>
       </c>
@@ -6513,7 +6513,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="9" spans="1:88">
+    <row r="9" spans="1:88" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>88</v>
       </c>
@@ -6776,7 +6776,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="10" spans="1:88">
+    <row r="10" spans="1:88" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>88</v>
       </c>
@@ -7039,7 +7039,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="11" spans="1:88">
+    <row r="11" spans="1:88" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>88</v>
       </c>
@@ -7302,7 +7302,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="12" spans="1:88" ht="15">
+    <row r="12" spans="1:88" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>88</v>
       </c>
@@ -7568,7 +7568,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="13" spans="1:88" ht="15">
+    <row r="13" spans="1:88" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>88</v>
       </c>
@@ -7834,7 +7834,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="14" spans="1:88">
+    <row r="14" spans="1:88" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>88</v>
       </c>
@@ -7851,16 +7851,16 @@
         <v>91</v>
       </c>
       <c r="F14" t="s">
-        <v>420</v>
+        <v>1120</v>
       </c>
       <c r="G14" t="s">
-        <v>421</v>
+        <v>1121</v>
       </c>
       <c r="H14" t="s">
         <v>94</v>
       </c>
       <c r="I14" s="1">
-        <v>37291</v>
+        <v>34880</v>
       </c>
       <c r="J14" t="s">
         <v>95</v>
@@ -7869,16 +7869,16 @@
         <v>96</v>
       </c>
       <c r="L14" t="s">
-        <v>97</v>
+        <v>305</v>
       </c>
       <c r="M14" t="s">
-        <v>422</v>
+        <v>106</v>
       </c>
       <c r="N14" t="s">
-        <v>423</v>
+        <v>1122</v>
       </c>
       <c r="O14" t="s">
-        <v>424</v>
+        <v>182</v>
       </c>
       <c r="P14" t="s">
         <v>262</v>
@@ -7887,13 +7887,13 @@
         <v>102</v>
       </c>
       <c r="R14" t="s">
-        <v>152</v>
+        <v>352</v>
       </c>
       <c r="S14" t="s">
         <v>104</v>
       </c>
       <c r="T14" s="2">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="U14" t="s">
         <v>105</v>
@@ -7911,19 +7911,19 @@
         <v>107</v>
       </c>
       <c r="Z14" t="s">
-        <v>107</v>
+        <v>184</v>
       </c>
       <c r="AA14" t="s">
         <v>108</v>
       </c>
       <c r="AB14" t="s">
-        <v>425</v>
+        <v>1123</v>
       </c>
       <c r="AC14" t="s">
         <v>110</v>
       </c>
       <c r="AD14" t="s">
-        <v>154</v>
+        <v>110</v>
       </c>
       <c r="AE14" t="s">
         <v>110</v>
@@ -7941,7 +7941,7 @@
         <v>106</v>
       </c>
       <c r="AJ14" t="s">
-        <v>426</v>
+        <v>1124</v>
       </c>
       <c r="AK14" t="s">
         <v>239</v>
@@ -7956,16 +7956,16 @@
         <v>114</v>
       </c>
       <c r="AO14" t="s">
-        <v>157</v>
+        <v>115</v>
       </c>
       <c r="AP14" t="s">
-        <v>116</v>
+        <v>309</v>
       </c>
       <c r="AQ14" t="s">
         <v>114</v>
       </c>
       <c r="AR14" t="s">
-        <v>427</v>
+        <v>1125</v>
       </c>
       <c r="AS14" t="s">
         <v>118</v>
@@ -7974,22 +7974,22 @@
         <v>106</v>
       </c>
       <c r="AU14" t="s">
-        <v>428</v>
+        <v>1126</v>
       </c>
       <c r="AV14" t="s">
         <v>106</v>
       </c>
       <c r="AW14" t="s">
-        <v>429</v>
+        <v>1127</v>
       </c>
       <c r="AX14" t="s">
-        <v>430</v>
+        <v>1128</v>
       </c>
       <c r="AY14" t="s">
-        <v>431</v>
+        <v>1129</v>
       </c>
       <c r="AZ14" t="s">
-        <v>120</v>
+        <v>1130</v>
       </c>
       <c r="BA14" t="s">
         <v>114</v>
@@ -8001,55 +8001,55 @@
         <v>114</v>
       </c>
       <c r="BD14" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="BE14" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="BF14" t="s">
         <v>125</v>
       </c>
       <c r="BG14" t="s">
-        <v>432</v>
+        <v>106</v>
       </c>
       <c r="BH14" t="s">
-        <v>433</v>
+        <v>1131</v>
       </c>
       <c r="BI14" t="s">
         <v>128</v>
       </c>
       <c r="BJ14" t="s">
-        <v>434</v>
+        <v>1132</v>
       </c>
       <c r="BK14" t="s">
         <v>128</v>
       </c>
       <c r="BL14" t="s">
-        <v>435</v>
+        <v>1133</v>
       </c>
       <c r="BM14" t="s">
         <v>128</v>
       </c>
       <c r="BN14" t="s">
-        <v>436</v>
+        <v>1134</v>
       </c>
       <c r="BO14" t="s">
         <v>128</v>
       </c>
       <c r="BP14" t="s">
-        <v>437</v>
+        <v>1135</v>
       </c>
       <c r="BQ14" t="s">
         <v>128</v>
       </c>
       <c r="BR14" t="s">
-        <v>438</v>
+        <v>1136</v>
       </c>
       <c r="BS14" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="BT14" t="s">
-        <v>439</v>
+        <v>1137</v>
       </c>
       <c r="BU14" t="s">
         <v>128</v>
@@ -8064,10 +8064,10 @@
         <v>138</v>
       </c>
       <c r="BY14" t="s">
-        <v>440</v>
+        <v>106</v>
       </c>
       <c r="BZ14" t="s">
-        <v>441</v>
+        <v>1138</v>
       </c>
       <c r="CA14" t="s">
         <v>102</v>
@@ -8097,7 +8097,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="15" spans="1:88">
+    <row r="15" spans="1:88" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>88</v>
       </c>
@@ -8361,7 +8361,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="16" spans="1:88">
+    <row r="16" spans="1:88" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>88</v>
       </c>
@@ -8627,7 +8627,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="17" spans="1:90">
+    <row r="17" spans="1:90" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>88</v>
       </c>
@@ -8644,16 +8644,16 @@
         <v>91</v>
       </c>
       <c r="F17" t="s">
-        <v>491</v>
+        <v>420</v>
       </c>
       <c r="G17" t="s">
-        <v>492</v>
+        <v>421</v>
       </c>
       <c r="H17" t="s">
         <v>94</v>
       </c>
       <c r="I17" s="1">
-        <v>35194</v>
+        <v>37291</v>
       </c>
       <c r="J17" t="s">
         <v>95</v>
@@ -8662,16 +8662,16 @@
         <v>96</v>
       </c>
       <c r="L17" t="s">
-        <v>260</v>
+        <v>97</v>
       </c>
       <c r="M17" t="s">
-        <v>106</v>
+        <v>422</v>
       </c>
       <c r="N17" t="s">
-        <v>493</v>
+        <v>423</v>
       </c>
       <c r="O17" t="s">
-        <v>494</v>
+        <v>424</v>
       </c>
       <c r="P17" t="s">
         <v>262</v>
@@ -8686,7 +8686,7 @@
         <v>104</v>
       </c>
       <c r="T17" s="2">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="U17" t="s">
         <v>105</v>
@@ -8698,31 +8698,31 @@
         <v>106</v>
       </c>
       <c r="X17" t="s">
-        <v>184</v>
+        <v>209</v>
       </c>
       <c r="Y17" t="s">
         <v>107</v>
       </c>
       <c r="Z17" t="s">
-        <v>209</v>
+        <v>107</v>
       </c>
       <c r="AA17" t="s">
         <v>108</v>
       </c>
       <c r="AB17" t="s">
-        <v>495</v>
+        <v>425</v>
       </c>
       <c r="AC17" t="s">
+        <v>110</v>
+      </c>
+      <c r="AD17" t="s">
         <v>154</v>
       </c>
-      <c r="AD17" t="s">
-        <v>111</v>
-      </c>
       <c r="AE17" t="s">
-        <v>154</v>
+        <v>110</v>
       </c>
       <c r="AF17" t="s">
-        <v>154</v>
+        <v>110</v>
       </c>
       <c r="AG17" t="s">
         <v>110</v>
@@ -8734,10 +8734,10 @@
         <v>106</v>
       </c>
       <c r="AJ17" t="s">
-        <v>155</v>
+        <v>426</v>
       </c>
       <c r="AK17" t="s">
-        <v>187</v>
+        <v>239</v>
       </c>
       <c r="AL17" t="s">
         <v>114</v>
@@ -8746,7 +8746,7 @@
         <v>114</v>
       </c>
       <c r="AN17" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="AO17" t="s">
         <v>157</v>
@@ -8758,7 +8758,7 @@
         <v>114</v>
       </c>
       <c r="AR17" t="s">
-        <v>496</v>
+        <v>427</v>
       </c>
       <c r="AS17" t="s">
         <v>118</v>
@@ -8767,22 +8767,22 @@
         <v>106</v>
       </c>
       <c r="AU17" t="s">
-        <v>497</v>
+        <v>428</v>
       </c>
       <c r="AV17" t="s">
         <v>106</v>
       </c>
       <c r="AW17" t="s">
-        <v>498</v>
+        <v>429</v>
       </c>
       <c r="AX17" t="s">
-        <v>499</v>
+        <v>430</v>
       </c>
       <c r="AY17" t="s">
-        <v>500</v>
+        <v>431</v>
       </c>
       <c r="AZ17" t="s">
-        <v>501</v>
+        <v>120</v>
       </c>
       <c r="BA17" t="s">
         <v>114</v>
@@ -8803,46 +8803,46 @@
         <v>125</v>
       </c>
       <c r="BG17" t="s">
-        <v>502</v>
+        <v>432</v>
       </c>
       <c r="BH17" t="s">
-        <v>503</v>
+        <v>433</v>
       </c>
       <c r="BI17" t="s">
         <v>128</v>
       </c>
       <c r="BJ17" t="s">
-        <v>504</v>
+        <v>434</v>
       </c>
       <c r="BK17" t="s">
+        <v>128</v>
+      </c>
+      <c r="BL17" t="s">
+        <v>435</v>
+      </c>
+      <c r="BM17" t="s">
+        <v>128</v>
+      </c>
+      <c r="BN17" t="s">
+        <v>436</v>
+      </c>
+      <c r="BO17" t="s">
+        <v>128</v>
+      </c>
+      <c r="BP17" t="s">
+        <v>437</v>
+      </c>
+      <c r="BQ17" t="s">
+        <v>128</v>
+      </c>
+      <c r="BR17" t="s">
+        <v>438</v>
+      </c>
+      <c r="BS17" t="s">
         <v>130</v>
       </c>
-      <c r="BL17" t="s">
-        <v>505</v>
-      </c>
-      <c r="BM17" t="s">
-        <v>128</v>
-      </c>
-      <c r="BN17" t="s">
-        <v>506</v>
-      </c>
-      <c r="BO17" t="s">
-        <v>128</v>
-      </c>
-      <c r="BP17" t="s">
-        <v>507</v>
-      </c>
-      <c r="BQ17" t="s">
-        <v>128</v>
-      </c>
-      <c r="BR17" t="s">
-        <v>508</v>
-      </c>
-      <c r="BS17" t="s">
-        <v>128</v>
-      </c>
       <c r="BT17" t="s">
-        <v>509</v>
+        <v>439</v>
       </c>
       <c r="BU17" t="s">
         <v>128</v>
@@ -8857,10 +8857,10 @@
         <v>138</v>
       </c>
       <c r="BY17" t="s">
-        <v>510</v>
+        <v>440</v>
       </c>
       <c r="BZ17" t="s">
-        <v>511</v>
+        <v>441</v>
       </c>
       <c r="CA17" t="s">
         <v>102</v>
@@ -8875,13 +8875,13 @@
         <v>102</v>
       </c>
       <c r="CE17" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="CF17" t="s">
         <v>227</v>
       </c>
       <c r="CG17" t="s">
-        <v>512</v>
+        <v>106</v>
       </c>
       <c r="CH17" t="s">
         <v>257</v>
@@ -8890,7 +8890,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="18" spans="1:90">
+    <row r="18" spans="1:90" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>88</v>
       </c>
@@ -8898,7 +8898,7 @@
         <v>46161</v>
       </c>
       <c r="C18" t="s">
-        <v>280</v>
+        <v>89</v>
       </c>
       <c r="D18" t="s">
         <v>90</v>
@@ -8907,16 +8907,16 @@
         <v>91</v>
       </c>
       <c r="F18" t="s">
-        <v>513</v>
+        <v>491</v>
       </c>
       <c r="G18" t="s">
-        <v>514</v>
+        <v>492</v>
       </c>
       <c r="H18" t="s">
         <v>94</v>
       </c>
       <c r="I18" s="1">
-        <v>38894</v>
+        <v>35194</v>
       </c>
       <c r="J18" t="s">
         <v>95</v>
@@ -8925,19 +8925,19 @@
         <v>96</v>
       </c>
       <c r="L18" t="s">
-        <v>305</v>
+        <v>260</v>
       </c>
       <c r="M18" t="s">
         <v>106</v>
       </c>
       <c r="N18" t="s">
-        <v>515</v>
+        <v>493</v>
       </c>
       <c r="O18" t="s">
-        <v>100</v>
+        <v>494</v>
       </c>
       <c r="P18" t="s">
-        <v>101</v>
+        <v>262</v>
       </c>
       <c r="Q18" t="s">
         <v>102</v>
@@ -8946,10 +8946,10 @@
         <v>152</v>
       </c>
       <c r="S18" t="s">
-        <v>236</v>
+        <v>104</v>
       </c>
       <c r="T18" s="2">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="U18" t="s">
         <v>105</v>
@@ -8961,31 +8961,31 @@
         <v>106</v>
       </c>
       <c r="X18" t="s">
-        <v>209</v>
+        <v>184</v>
       </c>
       <c r="Y18" t="s">
         <v>107</v>
       </c>
       <c r="Z18" t="s">
-        <v>184</v>
+        <v>209</v>
       </c>
       <c r="AA18" t="s">
-        <v>263</v>
+        <v>108</v>
       </c>
       <c r="AB18" t="s">
-        <v>106</v>
+        <v>495</v>
       </c>
       <c r="AC18" t="s">
-        <v>110</v>
+        <v>154</v>
       </c>
       <c r="AD18" t="s">
         <v>111</v>
       </c>
       <c r="AE18" t="s">
-        <v>110</v>
+        <v>154</v>
       </c>
       <c r="AF18" t="s">
-        <v>110</v>
+        <v>154</v>
       </c>
       <c r="AG18" t="s">
         <v>110</v>
@@ -8997,22 +8997,22 @@
         <v>106</v>
       </c>
       <c r="AJ18" t="s">
-        <v>472</v>
+        <v>155</v>
       </c>
       <c r="AK18" t="s">
-        <v>113</v>
+        <v>187</v>
       </c>
       <c r="AL18" t="s">
         <v>114</v>
       </c>
       <c r="AM18" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="AN18" t="s">
         <v>102</v>
       </c>
       <c r="AO18" t="s">
-        <v>115</v>
+        <v>157</v>
       </c>
       <c r="AP18" t="s">
         <v>116</v>
@@ -9021,7 +9021,7 @@
         <v>114</v>
       </c>
       <c r="AR18" t="s">
-        <v>516</v>
+        <v>496</v>
       </c>
       <c r="AS18" t="s">
         <v>118</v>
@@ -9030,22 +9030,22 @@
         <v>106</v>
       </c>
       <c r="AU18" t="s">
-        <v>517</v>
+        <v>497</v>
       </c>
       <c r="AV18" t="s">
-        <v>164</v>
+        <v>106</v>
       </c>
       <c r="AW18" t="s">
-        <v>518</v>
+        <v>498</v>
       </c>
       <c r="AX18" t="s">
-        <v>519</v>
+        <v>499</v>
       </c>
       <c r="AY18" t="s">
-        <v>520</v>
+        <v>500</v>
       </c>
       <c r="AZ18" t="s">
-        <v>164</v>
+        <v>501</v>
       </c>
       <c r="BA18" t="s">
         <v>114</v>
@@ -9066,46 +9066,46 @@
         <v>125</v>
       </c>
       <c r="BG18" t="s">
-        <v>293</v>
+        <v>502</v>
       </c>
       <c r="BH18" t="s">
-        <v>521</v>
+        <v>503</v>
       </c>
       <c r="BI18" t="s">
+        <v>128</v>
+      </c>
+      <c r="BJ18" t="s">
+        <v>504</v>
+      </c>
+      <c r="BK18" t="s">
         <v>130</v>
       </c>
-      <c r="BJ18" t="s">
-        <v>522</v>
-      </c>
-      <c r="BK18" t="s">
-        <v>128</v>
-      </c>
       <c r="BL18" t="s">
-        <v>523</v>
+        <v>505</v>
       </c>
       <c r="BM18" t="s">
         <v>128</v>
       </c>
       <c r="BN18" t="s">
-        <v>524</v>
+        <v>506</v>
       </c>
       <c r="BO18" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="BP18" t="s">
-        <v>525</v>
+        <v>507</v>
       </c>
       <c r="BQ18" t="s">
         <v>128</v>
       </c>
       <c r="BR18" t="s">
-        <v>526</v>
+        <v>508</v>
       </c>
       <c r="BS18" t="s">
         <v>128</v>
       </c>
       <c r="BT18" t="s">
-        <v>527</v>
+        <v>509</v>
       </c>
       <c r="BU18" t="s">
         <v>128</v>
@@ -9120,22 +9120,22 @@
         <v>138</v>
       </c>
       <c r="BY18" t="s">
-        <v>293</v>
+        <v>510</v>
       </c>
       <c r="BZ18" t="s">
-        <v>528</v>
+        <v>511</v>
       </c>
       <c r="CA18" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="CB18" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="CC18" t="s">
         <v>102</v>
       </c>
       <c r="CD18" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="CE18" t="s">
         <v>102</v>
@@ -9144,7 +9144,7 @@
         <v>227</v>
       </c>
       <c r="CG18" t="s">
-        <v>293</v>
+        <v>512</v>
       </c>
       <c r="CH18" t="s">
         <v>257</v>
@@ -9153,7 +9153,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="19" spans="1:90">
+    <row r="19" spans="1:90" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>88</v>
       </c>
@@ -9161,7 +9161,7 @@
         <v>46161</v>
       </c>
       <c r="C19" t="s">
-        <v>89</v>
+        <v>280</v>
       </c>
       <c r="D19" t="s">
         <v>90</v>
@@ -9170,16 +9170,16 @@
         <v>91</v>
       </c>
       <c r="F19" t="s">
-        <v>529</v>
+        <v>513</v>
       </c>
       <c r="G19" t="s">
-        <v>530</v>
+        <v>514</v>
       </c>
       <c r="H19" t="s">
         <v>94</v>
       </c>
       <c r="I19" s="1">
-        <v>33370</v>
+        <v>38894</v>
       </c>
       <c r="J19" t="s">
         <v>95</v>
@@ -9188,31 +9188,31 @@
         <v>96</v>
       </c>
       <c r="L19" t="s">
-        <v>260</v>
+        <v>305</v>
       </c>
       <c r="M19" t="s">
         <v>106</v>
       </c>
       <c r="N19" t="s">
-        <v>531</v>
+        <v>515</v>
       </c>
       <c r="O19" t="s">
-        <v>235</v>
+        <v>100</v>
       </c>
       <c r="P19" t="s">
-        <v>262</v>
+        <v>101</v>
       </c>
       <c r="Q19" t="s">
-        <v>446</v>
+        <v>102</v>
       </c>
       <c r="R19" t="s">
         <v>152</v>
       </c>
       <c r="S19" t="s">
-        <v>104</v>
+        <v>236</v>
       </c>
       <c r="T19" s="2">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="U19" t="s">
         <v>105</v>
@@ -9224,31 +9224,31 @@
         <v>106</v>
       </c>
       <c r="X19" t="s">
+        <v>209</v>
+      </c>
+      <c r="Y19" t="s">
         <v>107</v>
       </c>
-      <c r="Y19" t="s">
+      <c r="Z19" t="s">
         <v>184</v>
       </c>
-      <c r="Z19" t="s">
-        <v>107</v>
-      </c>
       <c r="AA19" t="s">
-        <v>447</v>
+        <v>263</v>
       </c>
       <c r="AB19" t="s">
-        <v>532</v>
+        <v>106</v>
       </c>
       <c r="AC19" t="s">
-        <v>154</v>
+        <v>110</v>
       </c>
       <c r="AD19" t="s">
+        <v>111</v>
+      </c>
+      <c r="AE19" t="s">
         <v>110</v>
       </c>
-      <c r="AE19" t="s">
-        <v>154</v>
-      </c>
       <c r="AF19" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="AG19" t="s">
         <v>110</v>
@@ -9260,22 +9260,22 @@
         <v>106</v>
       </c>
       <c r="AJ19" t="s">
-        <v>533</v>
+        <v>472</v>
       </c>
       <c r="AK19" t="s">
-        <v>187</v>
+        <v>113</v>
       </c>
       <c r="AL19" t="s">
         <v>114</v>
       </c>
       <c r="AM19" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="AN19" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="AO19" t="s">
-        <v>157</v>
+        <v>115</v>
       </c>
       <c r="AP19" t="s">
         <v>116</v>
@@ -9284,31 +9284,31 @@
         <v>114</v>
       </c>
       <c r="AR19" t="s">
-        <v>534</v>
+        <v>516</v>
       </c>
       <c r="AS19" t="s">
         <v>118</v>
       </c>
       <c r="AT19" t="s">
-        <v>535</v>
+        <v>106</v>
       </c>
       <c r="AU19" t="s">
-        <v>120</v>
+        <v>517</v>
       </c>
       <c r="AV19" t="s">
-        <v>106</v>
+        <v>164</v>
       </c>
       <c r="AW19" t="s">
-        <v>536</v>
+        <v>518</v>
       </c>
       <c r="AX19" t="s">
-        <v>537</v>
+        <v>519</v>
       </c>
       <c r="AY19" t="s">
-        <v>538</v>
+        <v>520</v>
       </c>
       <c r="AZ19" t="s">
-        <v>539</v>
+        <v>164</v>
       </c>
       <c r="BA19" t="s">
         <v>114</v>
@@ -9329,46 +9329,46 @@
         <v>125</v>
       </c>
       <c r="BG19" t="s">
-        <v>540</v>
+        <v>293</v>
       </c>
       <c r="BH19" t="s">
-        <v>541</v>
+        <v>521</v>
       </c>
       <c r="BI19" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="BJ19" t="s">
-        <v>542</v>
+        <v>522</v>
       </c>
       <c r="BK19" t="s">
+        <v>128</v>
+      </c>
+      <c r="BL19" t="s">
+        <v>523</v>
+      </c>
+      <c r="BM19" t="s">
+        <v>128</v>
+      </c>
+      <c r="BN19" t="s">
+        <v>524</v>
+      </c>
+      <c r="BO19" t="s">
         <v>130</v>
       </c>
-      <c r="BL19" t="s">
-        <v>543</v>
-      </c>
-      <c r="BM19" t="s">
-        <v>128</v>
-      </c>
-      <c r="BN19" t="s">
-        <v>544</v>
-      </c>
-      <c r="BO19" t="s">
-        <v>128</v>
-      </c>
       <c r="BP19" t="s">
-        <v>545</v>
+        <v>525</v>
       </c>
       <c r="BQ19" t="s">
         <v>128</v>
       </c>
       <c r="BR19" t="s">
-        <v>546</v>
+        <v>526</v>
       </c>
       <c r="BS19" t="s">
         <v>128</v>
       </c>
       <c r="BT19" t="s">
-        <v>547</v>
+        <v>527</v>
       </c>
       <c r="BU19" t="s">
         <v>128</v>
@@ -9383,16 +9383,16 @@
         <v>138</v>
       </c>
       <c r="BY19" t="s">
-        <v>106</v>
+        <v>293</v>
       </c>
       <c r="BZ19" t="s">
-        <v>548</v>
+        <v>528</v>
       </c>
       <c r="CA19" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="CB19" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="CC19" t="s">
         <v>102</v>
@@ -9401,13 +9401,13 @@
         <v>114</v>
       </c>
       <c r="CE19" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="CF19" t="s">
-        <v>140</v>
+        <v>227</v>
       </c>
       <c r="CG19" t="s">
-        <v>549</v>
+        <v>293</v>
       </c>
       <c r="CH19" t="s">
         <v>257</v>
@@ -9416,7 +9416,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="20" spans="1:90">
+    <row r="20" spans="1:90" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>88</v>
       </c>
@@ -9682,15 +9682,15 @@
         <v>144</v>
       </c>
     </row>
-    <row r="21" spans="1:90">
+    <row r="21" spans="1:90" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>88</v>
       </c>
       <c r="B21" s="1">
-        <v>46163</v>
+        <v>46161</v>
       </c>
       <c r="C21" t="s">
-        <v>347</v>
+        <v>89</v>
       </c>
       <c r="D21" t="s">
         <v>90</v>
@@ -9699,16 +9699,16 @@
         <v>91</v>
       </c>
       <c r="F21" t="s">
-        <v>570</v>
+        <v>529</v>
       </c>
       <c r="G21" t="s">
-        <v>571</v>
+        <v>530</v>
       </c>
       <c r="H21" t="s">
         <v>94</v>
       </c>
       <c r="I21" s="1">
-        <v>35155</v>
+        <v>33370</v>
       </c>
       <c r="J21" t="s">
         <v>95</v>
@@ -9717,31 +9717,31 @@
         <v>96</v>
       </c>
       <c r="L21" t="s">
-        <v>305</v>
+        <v>260</v>
       </c>
       <c r="M21" t="s">
         <v>106</v>
       </c>
       <c r="N21" t="s">
-        <v>572</v>
+        <v>531</v>
       </c>
       <c r="O21" t="s">
-        <v>424</v>
+        <v>235</v>
       </c>
       <c r="P21" t="s">
         <v>262</v>
       </c>
       <c r="Q21" t="s">
-        <v>102</v>
+        <v>446</v>
       </c>
       <c r="R21" t="s">
-        <v>352</v>
+        <v>152</v>
       </c>
       <c r="S21" t="s">
         <v>104</v>
       </c>
       <c r="T21" s="2">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="U21" t="s">
         <v>105</v>
@@ -9753,19 +9753,19 @@
         <v>106</v>
       </c>
       <c r="X21" t="s">
-        <v>209</v>
+        <v>107</v>
       </c>
       <c r="Y21" t="s">
+        <v>184</v>
+      </c>
+      <c r="Z21" t="s">
         <v>107</v>
       </c>
-      <c r="Z21" t="s">
-        <v>209</v>
-      </c>
       <c r="AA21" t="s">
-        <v>263</v>
+        <v>447</v>
       </c>
       <c r="AB21" t="s">
-        <v>106</v>
+        <v>532</v>
       </c>
       <c r="AC21" t="s">
         <v>154</v>
@@ -9774,10 +9774,10 @@
         <v>110</v>
       </c>
       <c r="AE21" t="s">
-        <v>110</v>
+        <v>154</v>
       </c>
       <c r="AF21" t="s">
-        <v>154</v>
+        <v>111</v>
       </c>
       <c r="AG21" t="s">
         <v>110</v>
@@ -9789,10 +9789,10 @@
         <v>106</v>
       </c>
       <c r="AJ21" t="s">
-        <v>573</v>
+        <v>533</v>
       </c>
       <c r="AK21" t="s">
-        <v>239</v>
+        <v>187</v>
       </c>
       <c r="AL21" t="s">
         <v>114</v>
@@ -9804,43 +9804,43 @@
         <v>114</v>
       </c>
       <c r="AO21" t="s">
-        <v>265</v>
+        <v>157</v>
       </c>
       <c r="AP21" t="s">
         <v>116</v>
       </c>
       <c r="AQ21" t="s">
-        <v>159</v>
+        <v>114</v>
       </c>
       <c r="AR21" t="s">
-        <v>106</v>
+        <v>534</v>
       </c>
       <c r="AS21" t="s">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="AT21" t="s">
-        <v>106</v>
+        <v>535</v>
       </c>
       <c r="AU21" t="s">
-        <v>574</v>
+        <v>120</v>
       </c>
       <c r="AV21" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="AW21" t="s">
-        <v>575</v>
+        <v>536</v>
       </c>
       <c r="AX21" t="s">
-        <v>576</v>
+        <v>537</v>
       </c>
       <c r="AY21" t="s">
-        <v>577</v>
+        <v>538</v>
       </c>
       <c r="AZ21" t="s">
-        <v>120</v>
+        <v>539</v>
       </c>
       <c r="BA21" t="s">
-        <v>246</v>
+        <v>114</v>
       </c>
       <c r="BB21" t="s">
         <v>114</v>
@@ -9858,46 +9858,46 @@
         <v>125</v>
       </c>
       <c r="BG21" t="s">
-        <v>578</v>
+        <v>540</v>
       </c>
       <c r="BH21" t="s">
-        <v>579</v>
+        <v>541</v>
       </c>
       <c r="BI21" t="s">
         <v>128</v>
       </c>
       <c r="BJ21" t="s">
-        <v>580</v>
+        <v>542</v>
       </c>
       <c r="BK21" t="s">
-        <v>167</v>
+        <v>130</v>
       </c>
       <c r="BL21" t="s">
-        <v>581</v>
+        <v>543</v>
       </c>
       <c r="BM21" t="s">
         <v>128</v>
       </c>
       <c r="BN21" t="s">
-        <v>582</v>
+        <v>544</v>
       </c>
       <c r="BO21" t="s">
         <v>128</v>
       </c>
       <c r="BP21" t="s">
-        <v>583</v>
+        <v>545</v>
       </c>
       <c r="BQ21" t="s">
         <v>128</v>
       </c>
       <c r="BR21" t="s">
-        <v>584</v>
+        <v>546</v>
       </c>
       <c r="BS21" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="BT21" t="s">
-        <v>585</v>
+        <v>547</v>
       </c>
       <c r="BU21" t="s">
         <v>128</v>
@@ -9912,40 +9912,40 @@
         <v>138</v>
       </c>
       <c r="BY21" t="s">
-        <v>586</v>
+        <v>106</v>
       </c>
       <c r="BZ21" t="s">
-        <v>587</v>
+        <v>548</v>
       </c>
       <c r="CA21" t="s">
         <v>102</v>
       </c>
       <c r="CB21" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="CC21" t="s">
         <v>102</v>
       </c>
       <c r="CD21" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="CE21" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="CF21" t="s">
-        <v>227</v>
+        <v>140</v>
       </c>
       <c r="CG21" t="s">
-        <v>588</v>
+        <v>549</v>
       </c>
       <c r="CH21" t="s">
-        <v>142</v>
+        <v>257</v>
       </c>
       <c r="CJ21" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="22" spans="1:90">
+    <row r="22" spans="1:90" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>88</v>
       </c>
@@ -10210,15 +10210,15 @@
       </c>
       <c r="CL22" s="9"/>
     </row>
-    <row r="23" spans="1:90">
+    <row r="23" spans="1:90" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>88</v>
       </c>
       <c r="B23" s="1">
-        <v>46162</v>
+        <v>46160</v>
       </c>
       <c r="C23" t="s">
-        <v>347</v>
+        <v>280</v>
       </c>
       <c r="D23" t="s">
         <v>90</v>
@@ -10227,16 +10227,16 @@
         <v>91</v>
       </c>
       <c r="F23" t="s">
-        <v>613</v>
+        <v>1079</v>
       </c>
       <c r="G23" t="s">
-        <v>614</v>
+        <v>1080</v>
       </c>
       <c r="H23" t="s">
         <v>94</v>
       </c>
       <c r="I23" s="1">
-        <v>34573</v>
+        <v>35098</v>
       </c>
       <c r="J23" t="s">
         <v>95</v>
@@ -10245,34 +10245,34 @@
         <v>96</v>
       </c>
       <c r="L23" t="s">
-        <v>97</v>
+        <v>305</v>
       </c>
       <c r="M23" t="s">
-        <v>591</v>
+        <v>106</v>
       </c>
       <c r="N23" t="s">
-        <v>615</v>
+        <v>1081</v>
       </c>
       <c r="O23" t="s">
-        <v>150</v>
+        <v>207</v>
       </c>
       <c r="P23" t="s">
-        <v>262</v>
+        <v>101</v>
       </c>
       <c r="Q23" t="s">
         <v>102</v>
       </c>
       <c r="R23" t="s">
-        <v>399</v>
+        <v>152</v>
       </c>
       <c r="S23" t="s">
         <v>236</v>
       </c>
       <c r="T23" s="2">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="U23" t="s">
-        <v>105</v>
+        <v>307</v>
       </c>
       <c r="V23" t="s">
         <v>106</v>
@@ -10281,31 +10281,31 @@
         <v>106</v>
       </c>
       <c r="X23" t="s">
-        <v>107</v>
+        <v>184</v>
       </c>
       <c r="Y23" t="s">
-        <v>107</v>
+        <v>184</v>
       </c>
       <c r="Z23" t="s">
-        <v>107</v>
+        <v>209</v>
       </c>
       <c r="AA23" t="s">
-        <v>447</v>
+        <v>263</v>
       </c>
       <c r="AB23" t="s">
-        <v>616</v>
+        <v>106</v>
       </c>
       <c r="AC23" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AD23" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AE23" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AF23" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AG23" t="s">
         <v>110</v>
@@ -10317,22 +10317,22 @@
         <v>106</v>
       </c>
       <c r="AJ23" t="s">
-        <v>617</v>
+        <v>1082</v>
       </c>
       <c r="AK23" t="s">
-        <v>187</v>
+        <v>239</v>
       </c>
       <c r="AL23" t="s">
         <v>114</v>
       </c>
       <c r="AM23" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="AN23" t="s">
         <v>114</v>
       </c>
       <c r="AO23" t="s">
-        <v>157</v>
+        <v>115</v>
       </c>
       <c r="AP23" t="s">
         <v>116</v>
@@ -10341,7 +10341,7 @@
         <v>114</v>
       </c>
       <c r="AR23" t="s">
-        <v>618</v>
+        <v>1083</v>
       </c>
       <c r="AS23" t="s">
         <v>118</v>
@@ -10350,22 +10350,22 @@
         <v>106</v>
       </c>
       <c r="AU23" t="s">
-        <v>619</v>
+        <v>1084</v>
       </c>
       <c r="AV23" t="s">
-        <v>120</v>
+        <v>1085</v>
       </c>
       <c r="AW23" t="s">
-        <v>620</v>
+        <v>1086</v>
       </c>
       <c r="AX23" t="s">
-        <v>621</v>
+        <v>1087</v>
       </c>
       <c r="AY23" t="s">
-        <v>622</v>
+        <v>1088</v>
       </c>
       <c r="AZ23" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="BA23" t="s">
         <v>114</v>
@@ -10374,7 +10374,7 @@
         <v>114</v>
       </c>
       <c r="BC23" t="s">
-        <v>114</v>
+        <v>246</v>
       </c>
       <c r="BD23" t="s">
         <v>102</v>
@@ -10386,46 +10386,46 @@
         <v>125</v>
       </c>
       <c r="BG23" t="s">
-        <v>623</v>
+        <v>1089</v>
       </c>
       <c r="BH23" t="s">
-        <v>624</v>
+        <v>1090</v>
       </c>
       <c r="BI23" t="s">
         <v>128</v>
       </c>
       <c r="BJ23" t="s">
-        <v>625</v>
+        <v>1091</v>
       </c>
       <c r="BK23" t="s">
         <v>128</v>
       </c>
       <c r="BL23" t="s">
-        <v>626</v>
+        <v>1092</v>
       </c>
       <c r="BM23" t="s">
         <v>128</v>
       </c>
       <c r="BN23" t="s">
-        <v>627</v>
+        <v>1093</v>
       </c>
       <c r="BO23" t="s">
         <v>128</v>
       </c>
       <c r="BP23" t="s">
-        <v>628</v>
+        <v>1094</v>
       </c>
       <c r="BQ23" t="s">
         <v>128</v>
       </c>
       <c r="BR23" t="s">
-        <v>629</v>
+        <v>1095</v>
       </c>
       <c r="BS23" t="s">
         <v>128</v>
       </c>
       <c r="BT23" t="s">
-        <v>630</v>
+        <v>1096</v>
       </c>
       <c r="BU23" t="s">
         <v>128</v>
@@ -10440,10 +10440,10 @@
         <v>138</v>
       </c>
       <c r="BY23" t="s">
-        <v>631</v>
+        <v>1097</v>
       </c>
       <c r="BZ23" t="s">
-        <v>632</v>
+        <v>1098</v>
       </c>
       <c r="CA23" t="s">
         <v>114</v>
@@ -10464,7 +10464,7 @@
         <v>140</v>
       </c>
       <c r="CG23" t="s">
-        <v>633</v>
+        <v>1099</v>
       </c>
       <c r="CH23" t="s">
         <v>257</v>
@@ -10473,15 +10473,15 @@
         <v>177</v>
       </c>
     </row>
-    <row r="24" spans="1:90">
+    <row r="24" spans="1:90" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>88</v>
       </c>
       <c r="B24" s="1">
-        <v>46162</v>
+        <v>46160</v>
       </c>
       <c r="C24" t="s">
-        <v>347</v>
+        <v>653</v>
       </c>
       <c r="D24" t="s">
         <v>90</v>
@@ -10490,34 +10490,34 @@
         <v>91</v>
       </c>
       <c r="F24" t="s">
-        <v>634</v>
+        <v>1100</v>
       </c>
       <c r="G24" t="s">
-        <v>635</v>
+        <v>1101</v>
       </c>
       <c r="H24" t="s">
         <v>94</v>
       </c>
       <c r="I24" s="1">
-        <v>37118</v>
+        <v>33408</v>
       </c>
       <c r="J24" t="s">
-        <v>95</v>
+        <v>232</v>
       </c>
       <c r="K24" t="s">
         <v>96</v>
       </c>
       <c r="L24" t="s">
-        <v>97</v>
+        <v>397</v>
       </c>
       <c r="M24" t="s">
-        <v>591</v>
+        <v>106</v>
       </c>
       <c r="N24" t="s">
-        <v>636</v>
+        <v>1102</v>
       </c>
       <c r="O24" t="s">
-        <v>424</v>
+        <v>182</v>
       </c>
       <c r="P24" t="s">
         <v>262</v>
@@ -10526,13 +10526,13 @@
         <v>102</v>
       </c>
       <c r="R24" t="s">
-        <v>352</v>
+        <v>183</v>
       </c>
       <c r="S24" t="s">
-        <v>208</v>
+        <v>236</v>
       </c>
       <c r="T24" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U24" t="s">
         <v>105</v>
@@ -10544,31 +10544,31 @@
         <v>106</v>
       </c>
       <c r="X24" t="s">
-        <v>107</v>
+        <v>209</v>
       </c>
       <c r="Y24" t="s">
-        <v>107</v>
+        <v>184</v>
       </c>
       <c r="Z24" t="s">
         <v>107</v>
       </c>
       <c r="AA24" t="s">
-        <v>108</v>
+        <v>447</v>
       </c>
       <c r="AB24" t="s">
-        <v>637</v>
+        <v>1103</v>
       </c>
       <c r="AC24" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="AD24" t="s">
         <v>111</v>
       </c>
       <c r="AE24" t="s">
-        <v>154</v>
+        <v>110</v>
       </c>
       <c r="AF24" t="s">
-        <v>154</v>
+        <v>110</v>
       </c>
       <c r="AG24" t="s">
         <v>110</v>
@@ -10580,13 +10580,13 @@
         <v>106</v>
       </c>
       <c r="AJ24" t="s">
-        <v>553</v>
+        <v>211</v>
       </c>
       <c r="AK24" t="s">
         <v>239</v>
       </c>
       <c r="AL24" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="AM24" t="s">
         <v>114</v>
@@ -10601,31 +10601,31 @@
         <v>212</v>
       </c>
       <c r="AQ24" t="s">
-        <v>159</v>
+        <v>114</v>
       </c>
       <c r="AR24" t="s">
-        <v>106</v>
+        <v>1104</v>
       </c>
       <c r="AS24" t="s">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="AT24" t="s">
         <v>106</v>
       </c>
       <c r="AU24" t="s">
-        <v>638</v>
+        <v>1105</v>
       </c>
       <c r="AV24" t="s">
         <v>120</v>
       </c>
       <c r="AW24" t="s">
-        <v>639</v>
+        <v>1106</v>
       </c>
       <c r="AX24" t="s">
-        <v>640</v>
+        <v>1107</v>
       </c>
       <c r="AY24" t="s">
-        <v>641</v>
+        <v>1108</v>
       </c>
       <c r="AZ24" t="s">
         <v>120</v>
@@ -10649,64 +10649,64 @@
         <v>125</v>
       </c>
       <c r="BG24" t="s">
-        <v>642</v>
+        <v>1109</v>
       </c>
       <c r="BH24" t="s">
-        <v>643</v>
+        <v>1110</v>
       </c>
       <c r="BI24" t="s">
         <v>128</v>
       </c>
       <c r="BJ24" t="s">
-        <v>644</v>
+        <v>1111</v>
       </c>
       <c r="BK24" t="s">
+        <v>167</v>
+      </c>
+      <c r="BL24" t="s">
+        <v>1112</v>
+      </c>
+      <c r="BM24" t="s">
+        <v>167</v>
+      </c>
+      <c r="BN24" t="s">
+        <v>1113</v>
+      </c>
+      <c r="BO24" t="s">
+        <v>167</v>
+      </c>
+      <c r="BP24" t="s">
+        <v>1114</v>
+      </c>
+      <c r="BQ24" t="s">
+        <v>128</v>
+      </c>
+      <c r="BR24" t="s">
+        <v>1115</v>
+      </c>
+      <c r="BS24" t="s">
         <v>130</v>
       </c>
-      <c r="BL24" t="s">
-        <v>645</v>
-      </c>
-      <c r="BM24" t="s">
-        <v>128</v>
-      </c>
-      <c r="BN24" t="s">
-        <v>646</v>
-      </c>
-      <c r="BO24" t="s">
-        <v>130</v>
-      </c>
-      <c r="BP24" t="s">
-        <v>647</v>
-      </c>
-      <c r="BQ24" t="s">
-        <v>128</v>
-      </c>
-      <c r="BR24" t="s">
-        <v>648</v>
-      </c>
-      <c r="BS24" t="s">
-        <v>128</v>
-      </c>
       <c r="BT24" t="s">
-        <v>649</v>
+        <v>1116</v>
       </c>
       <c r="BU24" t="s">
-        <v>128</v>
+        <v>167</v>
       </c>
       <c r="BV24" t="s">
-        <v>136</v>
+        <v>200</v>
       </c>
       <c r="BW24" t="s">
-        <v>137</v>
+        <v>200</v>
       </c>
       <c r="BX24" t="s">
-        <v>138</v>
+        <v>777</v>
       </c>
       <c r="BY24" t="s">
-        <v>650</v>
+        <v>1117</v>
       </c>
       <c r="BZ24" t="s">
-        <v>651</v>
+        <v>1118</v>
       </c>
       <c r="CA24" t="s">
         <v>102</v>
@@ -10718,33 +10718,33 @@
         <v>102</v>
       </c>
       <c r="CD24" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="CE24" t="s">
         <v>114</v>
       </c>
       <c r="CF24" t="s">
-        <v>140</v>
+        <v>227</v>
       </c>
       <c r="CG24" t="s">
-        <v>652</v>
+        <v>1119</v>
       </c>
       <c r="CH24" t="s">
-        <v>257</v>
+        <v>142</v>
       </c>
       <c r="CJ24" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="25" spans="1:90">
+    <row r="25" spans="1:90" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>88</v>
       </c>
       <c r="B25" s="1">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="C25" t="s">
-        <v>653</v>
+        <v>347</v>
       </c>
       <c r="D25" t="s">
         <v>90</v>
@@ -10753,49 +10753,49 @@
         <v>91</v>
       </c>
       <c r="F25" t="s">
-        <v>654</v>
+        <v>570</v>
       </c>
       <c r="G25" t="s">
-        <v>655</v>
+        <v>571</v>
       </c>
       <c r="H25" t="s">
         <v>94</v>
       </c>
       <c r="I25" s="1">
-        <v>36847</v>
+        <v>35155</v>
       </c>
       <c r="J25" t="s">
-        <v>232</v>
+        <v>95</v>
       </c>
       <c r="K25" t="s">
         <v>96</v>
       </c>
       <c r="L25" t="s">
-        <v>397</v>
+        <v>305</v>
       </c>
       <c r="M25" t="s">
         <v>106</v>
       </c>
       <c r="N25" t="s">
-        <v>656</v>
+        <v>572</v>
       </c>
       <c r="O25" t="s">
         <v>424</v>
       </c>
       <c r="P25" t="s">
-        <v>151</v>
+        <v>262</v>
       </c>
       <c r="Q25" t="s">
         <v>102</v>
       </c>
       <c r="R25" t="s">
-        <v>152</v>
+        <v>352</v>
       </c>
       <c r="S25" t="s">
-        <v>236</v>
+        <v>104</v>
       </c>
       <c r="T25" s="2">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="U25" t="s">
         <v>105</v>
@@ -10807,31 +10807,31 @@
         <v>106</v>
       </c>
       <c r="X25" t="s">
-        <v>184</v>
+        <v>209</v>
       </c>
       <c r="Y25" t="s">
-        <v>209</v>
+        <v>107</v>
       </c>
       <c r="Z25" t="s">
         <v>209</v>
       </c>
       <c r="AA25" t="s">
-        <v>108</v>
+        <v>263</v>
       </c>
       <c r="AB25" t="s">
-        <v>657</v>
+        <v>106</v>
       </c>
       <c r="AC25" t="s">
         <v>154</v>
       </c>
       <c r="AD25" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="AE25" t="s">
+        <v>110</v>
+      </c>
+      <c r="AF25" t="s">
         <v>154</v>
-      </c>
-      <c r="AF25" t="s">
-        <v>111</v>
       </c>
       <c r="AG25" t="s">
         <v>110</v>
@@ -10843,58 +10843,58 @@
         <v>106</v>
       </c>
       <c r="AJ25" t="s">
-        <v>658</v>
+        <v>573</v>
       </c>
       <c r="AK25" t="s">
-        <v>187</v>
+        <v>239</v>
       </c>
       <c r="AL25" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="AM25" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="AN25" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="AO25" t="s">
-        <v>115</v>
+        <v>265</v>
       </c>
       <c r="AP25" t="s">
-        <v>309</v>
+        <v>116</v>
       </c>
       <c r="AQ25" t="s">
-        <v>114</v>
+        <v>159</v>
       </c>
       <c r="AR25" t="s">
-        <v>659</v>
+        <v>106</v>
       </c>
       <c r="AS25" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="AT25" t="s">
         <v>106</v>
       </c>
       <c r="AU25" t="s">
-        <v>660</v>
+        <v>574</v>
       </c>
       <c r="AV25" t="s">
-        <v>661</v>
+        <v>120</v>
       </c>
       <c r="AW25" t="s">
-        <v>662</v>
+        <v>575</v>
       </c>
       <c r="AX25" t="s">
-        <v>663</v>
+        <v>576</v>
       </c>
       <c r="AY25" t="s">
-        <v>664</v>
+        <v>577</v>
       </c>
       <c r="AZ25" t="s">
-        <v>665</v>
+        <v>120</v>
       </c>
       <c r="BA25" t="s">
-        <v>114</v>
+        <v>246</v>
       </c>
       <c r="BB25" t="s">
         <v>114</v>
@@ -10903,55 +10903,55 @@
         <v>114</v>
       </c>
       <c r="BD25" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="BE25" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="BF25" t="s">
         <v>125</v>
       </c>
       <c r="BG25" t="s">
-        <v>666</v>
+        <v>578</v>
       </c>
       <c r="BH25" t="s">
-        <v>667</v>
+        <v>579</v>
       </c>
       <c r="BI25" t="s">
         <v>128</v>
       </c>
       <c r="BJ25" t="s">
-        <v>668</v>
+        <v>580</v>
       </c>
       <c r="BK25" t="s">
+        <v>167</v>
+      </c>
+      <c r="BL25" t="s">
+        <v>581</v>
+      </c>
+      <c r="BM25" t="s">
+        <v>128</v>
+      </c>
+      <c r="BN25" t="s">
+        <v>582</v>
+      </c>
+      <c r="BO25" t="s">
+        <v>128</v>
+      </c>
+      <c r="BP25" t="s">
+        <v>583</v>
+      </c>
+      <c r="BQ25" t="s">
+        <v>128</v>
+      </c>
+      <c r="BR25" t="s">
+        <v>584</v>
+      </c>
+      <c r="BS25" t="s">
         <v>130</v>
       </c>
-      <c r="BL25" t="s">
-        <v>669</v>
-      </c>
-      <c r="BM25" t="s">
-        <v>128</v>
-      </c>
-      <c r="BN25" t="s">
-        <v>670</v>
-      </c>
-      <c r="BO25" t="s">
-        <v>130</v>
-      </c>
-      <c r="BP25" t="s">
-        <v>671</v>
-      </c>
-      <c r="BQ25" t="s">
-        <v>130</v>
-      </c>
-      <c r="BR25" t="s">
-        <v>672</v>
-      </c>
-      <c r="BS25" t="s">
-        <v>128</v>
-      </c>
       <c r="BT25" t="s">
-        <v>673</v>
+        <v>585</v>
       </c>
       <c r="BU25" t="s">
         <v>128</v>
@@ -10966,10 +10966,10 @@
         <v>138</v>
       </c>
       <c r="BY25" t="s">
-        <v>674</v>
+        <v>586</v>
       </c>
       <c r="BZ25" t="s">
-        <v>675</v>
+        <v>587</v>
       </c>
       <c r="CA25" t="s">
         <v>102</v>
@@ -10981,25 +10981,25 @@
         <v>102</v>
       </c>
       <c r="CD25" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="CE25" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="CF25" t="s">
         <v>227</v>
       </c>
       <c r="CG25" t="s">
-        <v>676</v>
+        <v>588</v>
       </c>
       <c r="CH25" t="s">
-        <v>257</v>
+        <v>142</v>
       </c>
       <c r="CJ25" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="26" spans="1:90">
+    <row r="26" spans="1:90" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>88</v>
       </c>
@@ -11007,7 +11007,7 @@
         <v>46162</v>
       </c>
       <c r="C26" t="s">
-        <v>280</v>
+        <v>347</v>
       </c>
       <c r="D26" t="s">
         <v>90</v>
@@ -11016,16 +11016,16 @@
         <v>91</v>
       </c>
       <c r="F26" t="s">
-        <v>677</v>
+        <v>613</v>
       </c>
       <c r="G26" t="s">
-        <v>678</v>
+        <v>614</v>
       </c>
       <c r="H26" t="s">
         <v>94</v>
       </c>
       <c r="I26" s="1">
-        <v>35908</v>
+        <v>34573</v>
       </c>
       <c r="J26" t="s">
         <v>95</v>
@@ -11034,31 +11034,31 @@
         <v>96</v>
       </c>
       <c r="L26" t="s">
-        <v>397</v>
+        <v>97</v>
       </c>
       <c r="M26" t="s">
-        <v>106</v>
+        <v>591</v>
       </c>
       <c r="N26" t="s">
-        <v>679</v>
+        <v>615</v>
       </c>
       <c r="O26" t="s">
-        <v>235</v>
+        <v>150</v>
       </c>
       <c r="P26" t="s">
-        <v>101</v>
+        <v>262</v>
       </c>
       <c r="Q26" t="s">
-        <v>446</v>
+        <v>102</v>
       </c>
       <c r="R26" t="s">
-        <v>152</v>
+        <v>399</v>
       </c>
       <c r="S26" t="s">
         <v>236</v>
       </c>
       <c r="T26" s="2">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="U26" t="s">
         <v>105</v>
@@ -11079,22 +11079,22 @@
         <v>107</v>
       </c>
       <c r="AA26" t="s">
-        <v>108</v>
+        <v>447</v>
       </c>
       <c r="AB26" t="s">
-        <v>680</v>
+        <v>616</v>
       </c>
       <c r="AC26" t="s">
         <v>110</v>
       </c>
       <c r="AD26" t="s">
-        <v>154</v>
+        <v>110</v>
       </c>
       <c r="AE26" t="s">
-        <v>154</v>
+        <v>110</v>
       </c>
       <c r="AF26" t="s">
-        <v>154</v>
+        <v>110</v>
       </c>
       <c r="AG26" t="s">
         <v>110</v>
@@ -11106,10 +11106,10 @@
         <v>106</v>
       </c>
       <c r="AJ26" t="s">
-        <v>681</v>
+        <v>617</v>
       </c>
       <c r="AK26" t="s">
-        <v>239</v>
+        <v>187</v>
       </c>
       <c r="AL26" t="s">
         <v>114</v>
@@ -11130,7 +11130,7 @@
         <v>114</v>
       </c>
       <c r="AR26" t="s">
-        <v>682</v>
+        <v>618</v>
       </c>
       <c r="AS26" t="s">
         <v>118</v>
@@ -11139,22 +11139,22 @@
         <v>106</v>
       </c>
       <c r="AU26" t="s">
-        <v>683</v>
+        <v>619</v>
       </c>
       <c r="AV26" t="s">
-        <v>684</v>
+        <v>120</v>
       </c>
       <c r="AW26" t="s">
-        <v>685</v>
+        <v>620</v>
       </c>
       <c r="AX26" t="s">
-        <v>686</v>
+        <v>621</v>
       </c>
       <c r="AY26" t="s">
-        <v>687</v>
+        <v>622</v>
       </c>
       <c r="AZ26" t="s">
-        <v>688</v>
+        <v>120</v>
       </c>
       <c r="BA26" t="s">
         <v>114</v>
@@ -11166,55 +11166,55 @@
         <v>114</v>
       </c>
       <c r="BD26" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="BE26" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="BF26" t="s">
         <v>125</v>
       </c>
       <c r="BG26" t="s">
-        <v>689</v>
+        <v>623</v>
       </c>
       <c r="BH26" t="s">
-        <v>690</v>
+        <v>624</v>
       </c>
       <c r="BI26" t="s">
         <v>128</v>
       </c>
       <c r="BJ26" t="s">
-        <v>691</v>
+        <v>625</v>
       </c>
       <c r="BK26" t="s">
         <v>128</v>
       </c>
       <c r="BL26" t="s">
-        <v>692</v>
+        <v>626</v>
       </c>
       <c r="BM26" t="s">
         <v>128</v>
       </c>
       <c r="BN26" t="s">
-        <v>693</v>
+        <v>627</v>
       </c>
       <c r="BO26" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="BP26" t="s">
-        <v>694</v>
+        <v>628</v>
       </c>
       <c r="BQ26" t="s">
         <v>128</v>
       </c>
       <c r="BR26" t="s">
-        <v>695</v>
+        <v>629</v>
       </c>
       <c r="BS26" t="s">
         <v>128</v>
       </c>
       <c r="BT26" t="s">
-        <v>696</v>
+        <v>630</v>
       </c>
       <c r="BU26" t="s">
         <v>128</v>
@@ -11229,22 +11229,22 @@
         <v>138</v>
       </c>
       <c r="BY26" t="s">
-        <v>567</v>
+        <v>631</v>
       </c>
       <c r="BZ26" t="s">
-        <v>697</v>
+        <v>632</v>
       </c>
       <c r="CA26" t="s">
         <v>114</v>
       </c>
       <c r="CB26" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="CC26" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="CD26" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="CE26" t="s">
         <v>114</v>
@@ -11253,7 +11253,7 @@
         <v>140</v>
       </c>
       <c r="CG26" t="s">
-        <v>698</v>
+        <v>633</v>
       </c>
       <c r="CH26" t="s">
         <v>257</v>
@@ -11262,7 +11262,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="27" spans="1:90">
+    <row r="27" spans="1:90" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>88</v>
       </c>
@@ -11528,7 +11528,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="28" spans="1:90">
+    <row r="28" spans="1:90" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>88</v>
       </c>
@@ -11792,15 +11792,15 @@
         <v>466</v>
       </c>
     </row>
-    <row r="29" spans="1:90">
+    <row r="29" spans="1:90" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>88</v>
       </c>
       <c r="B29" s="1">
-        <v>46156</v>
+        <v>46162</v>
       </c>
       <c r="C29" t="s">
-        <v>653</v>
+        <v>347</v>
       </c>
       <c r="D29" t="s">
         <v>90</v>
@@ -11809,16 +11809,16 @@
         <v>91</v>
       </c>
       <c r="F29" t="s">
-        <v>738</v>
+        <v>634</v>
       </c>
       <c r="G29" t="s">
-        <v>739</v>
+        <v>635</v>
       </c>
       <c r="H29" t="s">
         <v>94</v>
       </c>
       <c r="I29" s="1">
-        <v>33812</v>
+        <v>37118</v>
       </c>
       <c r="J29" t="s">
         <v>95</v>
@@ -11827,13 +11827,13 @@
         <v>96</v>
       </c>
       <c r="L29" t="s">
-        <v>148</v>
+        <v>97</v>
       </c>
       <c r="M29" t="s">
-        <v>106</v>
+        <v>591</v>
       </c>
       <c r="N29" t="s">
-        <v>740</v>
+        <v>636</v>
       </c>
       <c r="O29" t="s">
         <v>424</v>
@@ -11842,16 +11842,16 @@
         <v>262</v>
       </c>
       <c r="Q29" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="R29" t="s">
-        <v>183</v>
+        <v>352</v>
       </c>
       <c r="S29" t="s">
-        <v>236</v>
+        <v>208</v>
       </c>
       <c r="T29" s="2">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="U29" t="s">
         <v>105</v>
@@ -11863,10 +11863,10 @@
         <v>106</v>
       </c>
       <c r="X29" t="s">
-        <v>209</v>
+        <v>107</v>
       </c>
       <c r="Y29" t="s">
-        <v>184</v>
+        <v>107</v>
       </c>
       <c r="Z29" t="s">
         <v>107</v>
@@ -11875,19 +11875,19 @@
         <v>108</v>
       </c>
       <c r="AB29" t="s">
-        <v>741</v>
+        <v>637</v>
       </c>
       <c r="AC29" t="s">
         <v>111</v>
       </c>
       <c r="AD29" t="s">
+        <v>111</v>
+      </c>
+      <c r="AE29" t="s">
         <v>154</v>
       </c>
-      <c r="AE29" t="s">
-        <v>110</v>
-      </c>
       <c r="AF29" t="s">
-        <v>111</v>
+        <v>154</v>
       </c>
       <c r="AG29" t="s">
         <v>110</v>
@@ -11899,10 +11899,10 @@
         <v>106</v>
       </c>
       <c r="AJ29" t="s">
-        <v>658</v>
+        <v>553</v>
       </c>
       <c r="AK29" t="s">
-        <v>187</v>
+        <v>239</v>
       </c>
       <c r="AL29" t="s">
         <v>114</v>
@@ -11911,40 +11911,40 @@
         <v>114</v>
       </c>
       <c r="AN29" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="AO29" t="s">
-        <v>265</v>
+        <v>157</v>
       </c>
       <c r="AP29" t="s">
-        <v>309</v>
+        <v>212</v>
       </c>
       <c r="AQ29" t="s">
-        <v>114</v>
+        <v>159</v>
       </c>
       <c r="AR29" t="s">
-        <v>742</v>
+        <v>106</v>
       </c>
       <c r="AS29" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="AT29" t="s">
         <v>106</v>
       </c>
       <c r="AU29" t="s">
-        <v>743</v>
+        <v>638</v>
       </c>
       <c r="AV29" t="s">
         <v>120</v>
       </c>
       <c r="AW29" t="s">
-        <v>744</v>
+        <v>639</v>
       </c>
       <c r="AX29" t="s">
-        <v>745</v>
+        <v>640</v>
       </c>
       <c r="AY29" t="s">
-        <v>746</v>
+        <v>641</v>
       </c>
       <c r="AZ29" t="s">
         <v>120</v>
@@ -11968,46 +11968,46 @@
         <v>125</v>
       </c>
       <c r="BG29" t="s">
-        <v>747</v>
+        <v>642</v>
       </c>
       <c r="BH29" t="s">
-        <v>748</v>
+        <v>643</v>
       </c>
       <c r="BI29" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="BJ29" t="s">
-        <v>749</v>
+        <v>644</v>
       </c>
       <c r="BK29" t="s">
         <v>130</v>
       </c>
       <c r="BL29" t="s">
-        <v>750</v>
+        <v>645</v>
       </c>
       <c r="BM29" t="s">
         <v>128</v>
       </c>
       <c r="BN29" t="s">
-        <v>751</v>
+        <v>646</v>
       </c>
       <c r="BO29" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="BP29" t="s">
-        <v>752</v>
+        <v>647</v>
       </c>
       <c r="BQ29" t="s">
         <v>128</v>
       </c>
       <c r="BR29" t="s">
-        <v>753</v>
+        <v>648</v>
       </c>
       <c r="BS29" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="BT29" t="s">
-        <v>754</v>
+        <v>649</v>
       </c>
       <c r="BU29" t="s">
         <v>128</v>
@@ -12022,48 +12022,48 @@
         <v>138</v>
       </c>
       <c r="BY29" t="s">
-        <v>755</v>
+        <v>650</v>
       </c>
       <c r="BZ29" t="s">
-        <v>756</v>
+        <v>651</v>
       </c>
       <c r="CA29" t="s">
         <v>102</v>
       </c>
       <c r="CB29" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="CC29" t="s">
         <v>102</v>
       </c>
       <c r="CD29" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="CE29" t="s">
         <v>114</v>
       </c>
       <c r="CF29" t="s">
-        <v>227</v>
+        <v>140</v>
       </c>
       <c r="CG29" t="s">
-        <v>757</v>
+        <v>652</v>
       </c>
       <c r="CH29" t="s">
-        <v>142</v>
+        <v>257</v>
       </c>
       <c r="CJ29" t="s">
-        <v>177</v>
+        <v>144</v>
       </c>
     </row>
-    <row r="30" spans="1:90">
+    <row r="30" spans="1:90" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>88</v>
       </c>
       <c r="B30" s="1">
-        <v>46163</v>
+        <v>46162</v>
       </c>
       <c r="C30" t="s">
-        <v>145</v>
+        <v>653</v>
       </c>
       <c r="D30" t="s">
         <v>90</v>
@@ -12072,19 +12072,19 @@
         <v>91</v>
       </c>
       <c r="F30" t="s">
-        <v>758</v>
+        <v>654</v>
       </c>
       <c r="G30" t="s">
-        <v>759</v>
+        <v>655</v>
       </c>
       <c r="H30" t="s">
         <v>94</v>
       </c>
       <c r="I30" s="1">
-        <v>35779</v>
+        <v>36847</v>
       </c>
       <c r="J30" t="s">
-        <v>95</v>
+        <v>232</v>
       </c>
       <c r="K30" t="s">
         <v>96</v>
@@ -12096,13 +12096,13 @@
         <v>106</v>
       </c>
       <c r="N30" t="s">
-        <v>760</v>
+        <v>656</v>
       </c>
       <c r="O30" t="s">
-        <v>182</v>
+        <v>424</v>
       </c>
       <c r="P30" t="s">
-        <v>101</v>
+        <v>151</v>
       </c>
       <c r="Q30" t="s">
         <v>102</v>
@@ -12114,7 +12114,7 @@
         <v>236</v>
       </c>
       <c r="T30" s="2">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="U30" t="s">
         <v>105</v>
@@ -12126,28 +12126,28 @@
         <v>106</v>
       </c>
       <c r="X30" t="s">
+        <v>184</v>
+      </c>
+      <c r="Y30" t="s">
         <v>209</v>
       </c>
-      <c r="Y30" t="s">
-        <v>107</v>
-      </c>
       <c r="Z30" t="s">
-        <v>107</v>
+        <v>209</v>
       </c>
       <c r="AA30" t="s">
-        <v>447</v>
+        <v>108</v>
       </c>
       <c r="AB30" t="s">
-        <v>761</v>
+        <v>657</v>
       </c>
       <c r="AC30" t="s">
         <v>154</v>
       </c>
       <c r="AD30" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AE30" t="s">
-        <v>110</v>
+        <v>154</v>
       </c>
       <c r="AF30" t="s">
         <v>111</v>
@@ -12162,31 +12162,31 @@
         <v>106</v>
       </c>
       <c r="AJ30" t="s">
-        <v>762</v>
+        <v>658</v>
       </c>
       <c r="AK30" t="s">
         <v>187</v>
       </c>
       <c r="AL30" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="AM30" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="AN30" t="s">
         <v>102</v>
       </c>
       <c r="AO30" t="s">
-        <v>157</v>
+        <v>115</v>
       </c>
       <c r="AP30" t="s">
-        <v>116</v>
+        <v>309</v>
       </c>
       <c r="AQ30" t="s">
-        <v>159</v>
+        <v>114</v>
       </c>
       <c r="AR30" t="s">
-        <v>106</v>
+        <v>659</v>
       </c>
       <c r="AS30" t="s">
         <v>118</v>
@@ -12195,22 +12195,22 @@
         <v>106</v>
       </c>
       <c r="AU30" t="s">
-        <v>763</v>
+        <v>660</v>
       </c>
       <c r="AV30" t="s">
-        <v>764</v>
+        <v>661</v>
       </c>
       <c r="AW30" t="s">
-        <v>765</v>
+        <v>662</v>
       </c>
       <c r="AX30" t="s">
-        <v>766</v>
+        <v>663</v>
       </c>
       <c r="AY30" t="s">
-        <v>767</v>
+        <v>664</v>
       </c>
       <c r="AZ30" t="s">
-        <v>768</v>
+        <v>665</v>
       </c>
       <c r="BA30" t="s">
         <v>114</v>
@@ -12231,94 +12231,94 @@
         <v>125</v>
       </c>
       <c r="BG30" t="s">
-        <v>769</v>
+        <v>666</v>
       </c>
       <c r="BH30" t="s">
-        <v>770</v>
+        <v>667</v>
       </c>
       <c r="BI30" t="s">
-        <v>167</v>
+        <v>128</v>
       </c>
       <c r="BJ30" t="s">
-        <v>771</v>
+        <v>668</v>
       </c>
       <c r="BK30" t="s">
-        <v>167</v>
+        <v>130</v>
       </c>
       <c r="BL30" t="s">
-        <v>772</v>
+        <v>669</v>
       </c>
       <c r="BM30" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="BN30" t="s">
-        <v>773</v>
+        <v>670</v>
       </c>
       <c r="BO30" t="s">
         <v>130</v>
       </c>
       <c r="BP30" t="s">
-        <v>774</v>
+        <v>671</v>
       </c>
       <c r="BQ30" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="BR30" t="s">
-        <v>775</v>
+        <v>672</v>
       </c>
       <c r="BS30" t="s">
-        <v>167</v>
+        <v>128</v>
       </c>
       <c r="BT30" t="s">
-        <v>776</v>
+        <v>673</v>
       </c>
       <c r="BU30" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="BV30" t="s">
-        <v>200</v>
+        <v>136</v>
       </c>
       <c r="BW30" t="s">
-        <v>200</v>
+        <v>137</v>
       </c>
       <c r="BX30" t="s">
-        <v>777</v>
+        <v>138</v>
       </c>
       <c r="BY30" t="s">
-        <v>778</v>
+        <v>674</v>
       </c>
       <c r="BZ30" t="s">
-        <v>779</v>
+        <v>675</v>
       </c>
       <c r="CA30" t="s">
         <v>102</v>
       </c>
       <c r="CB30" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="CC30" t="s">
         <v>102</v>
       </c>
       <c r="CD30" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="CE30" t="s">
         <v>114</v>
       </c>
       <c r="CF30" t="s">
-        <v>140</v>
+        <v>227</v>
       </c>
       <c r="CG30" t="s">
-        <v>780</v>
+        <v>676</v>
       </c>
       <c r="CH30" t="s">
-        <v>142</v>
+        <v>257</v>
       </c>
       <c r="CJ30" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="31" spans="1:90">
+    <row r="31" spans="1:90" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>88</v>
       </c>
@@ -12582,7 +12582,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="32" spans="1:90">
+    <row r="32" spans="1:90" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>88</v>
       </c>
@@ -12846,7 +12846,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="33" spans="1:88">
+    <row r="33" spans="1:88" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>88</v>
       </c>
@@ -12863,16 +12863,16 @@
         <v>91</v>
       </c>
       <c r="F33" t="s">
-        <v>820</v>
+        <v>677</v>
       </c>
       <c r="G33" t="s">
-        <v>821</v>
+        <v>678</v>
       </c>
       <c r="H33" t="s">
         <v>94</v>
       </c>
       <c r="I33" s="1">
-        <v>34741</v>
+        <v>35908</v>
       </c>
       <c r="J33" t="s">
         <v>95</v>
@@ -12881,31 +12881,31 @@
         <v>96</v>
       </c>
       <c r="L33" t="s">
-        <v>822</v>
+        <v>397</v>
       </c>
       <c r="M33" t="s">
         <v>106</v>
       </c>
       <c r="N33" t="s">
-        <v>823</v>
+        <v>679</v>
       </c>
       <c r="O33" t="s">
-        <v>100</v>
+        <v>235</v>
       </c>
       <c r="P33" t="s">
-        <v>262</v>
+        <v>101</v>
       </c>
       <c r="Q33" t="s">
-        <v>102</v>
+        <v>446</v>
       </c>
       <c r="R33" t="s">
-        <v>183</v>
+        <v>152</v>
       </c>
       <c r="S33" t="s">
-        <v>104</v>
+        <v>236</v>
       </c>
       <c r="T33" s="2">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="U33" t="s">
         <v>105</v>
@@ -12923,13 +12923,13 @@
         <v>107</v>
       </c>
       <c r="Z33" t="s">
-        <v>184</v>
+        <v>107</v>
       </c>
       <c r="AA33" t="s">
         <v>108</v>
       </c>
       <c r="AB33" t="s">
-        <v>824</v>
+        <v>680</v>
       </c>
       <c r="AC33" t="s">
         <v>110</v>
@@ -12941,7 +12941,7 @@
         <v>154</v>
       </c>
       <c r="AF33" t="s">
-        <v>110</v>
+        <v>154</v>
       </c>
       <c r="AG33" t="s">
         <v>110</v>
@@ -12953,22 +12953,22 @@
         <v>106</v>
       </c>
       <c r="AJ33" t="s">
-        <v>825</v>
+        <v>681</v>
       </c>
       <c r="AK33" t="s">
-        <v>113</v>
+        <v>239</v>
       </c>
       <c r="AL33" t="s">
         <v>114</v>
       </c>
       <c r="AM33" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="AN33" t="s">
         <v>114</v>
       </c>
       <c r="AO33" t="s">
-        <v>265</v>
+        <v>157</v>
       </c>
       <c r="AP33" t="s">
         <v>116</v>
@@ -12977,7 +12977,7 @@
         <v>114</v>
       </c>
       <c r="AR33" t="s">
-        <v>826</v>
+        <v>682</v>
       </c>
       <c r="AS33" t="s">
         <v>118</v>
@@ -12986,22 +12986,22 @@
         <v>106</v>
       </c>
       <c r="AU33" t="s">
-        <v>827</v>
+        <v>683</v>
       </c>
       <c r="AV33" t="s">
         <v>684</v>
       </c>
       <c r="AW33" t="s">
-        <v>828</v>
+        <v>685</v>
       </c>
       <c r="AX33" t="s">
-        <v>829</v>
+        <v>686</v>
       </c>
       <c r="AY33" t="s">
-        <v>830</v>
+        <v>687</v>
       </c>
       <c r="AZ33" t="s">
-        <v>831</v>
+        <v>688</v>
       </c>
       <c r="BA33" t="s">
         <v>114</v>
@@ -13022,46 +13022,46 @@
         <v>125</v>
       </c>
       <c r="BG33" t="s">
-        <v>832</v>
+        <v>689</v>
       </c>
       <c r="BH33" t="s">
-        <v>833</v>
+        <v>690</v>
       </c>
       <c r="BI33" t="s">
         <v>128</v>
       </c>
       <c r="BJ33" t="s">
-        <v>834</v>
+        <v>691</v>
       </c>
       <c r="BK33" t="s">
         <v>128</v>
       </c>
       <c r="BL33" t="s">
-        <v>835</v>
+        <v>692</v>
       </c>
       <c r="BM33" t="s">
         <v>128</v>
       </c>
       <c r="BN33" t="s">
-        <v>836</v>
+        <v>693</v>
       </c>
       <c r="BO33" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="BP33" t="s">
-        <v>837</v>
+        <v>694</v>
       </c>
       <c r="BQ33" t="s">
         <v>128</v>
       </c>
       <c r="BR33" t="s">
-        <v>838</v>
+        <v>695</v>
       </c>
       <c r="BS33" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="BT33" t="s">
-        <v>839</v>
+        <v>696</v>
       </c>
       <c r="BU33" t="s">
         <v>128</v>
@@ -13076,19 +13076,19 @@
         <v>138</v>
       </c>
       <c r="BY33" t="s">
-        <v>832</v>
+        <v>567</v>
       </c>
       <c r="BZ33" t="s">
-        <v>840</v>
+        <v>697</v>
       </c>
       <c r="CA33" t="s">
         <v>114</v>
       </c>
       <c r="CB33" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="CC33" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="CD33" t="s">
         <v>102</v>
@@ -13100,24 +13100,24 @@
         <v>140</v>
       </c>
       <c r="CG33" t="s">
-        <v>841</v>
+        <v>698</v>
       </c>
       <c r="CH33" t="s">
-        <v>142</v>
+        <v>257</v>
       </c>
       <c r="CJ33" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="34" spans="1:88">
+    <row r="34" spans="1:88" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>88</v>
       </c>
       <c r="B34" s="1">
-        <v>46162</v>
+        <v>46156</v>
       </c>
       <c r="C34" t="s">
-        <v>145</v>
+        <v>653</v>
       </c>
       <c r="D34" t="s">
         <v>90</v>
@@ -13126,16 +13126,16 @@
         <v>91</v>
       </c>
       <c r="F34" t="s">
-        <v>842</v>
+        <v>738</v>
       </c>
       <c r="G34" t="s">
-        <v>843</v>
+        <v>739</v>
       </c>
       <c r="H34" t="s">
         <v>94</v>
       </c>
       <c r="I34" s="1">
-        <v>35687</v>
+        <v>33812</v>
       </c>
       <c r="J34" t="s">
         <v>95</v>
@@ -13144,31 +13144,31 @@
         <v>96</v>
       </c>
       <c r="L34" t="s">
-        <v>97</v>
+        <v>148</v>
       </c>
       <c r="M34" t="s">
-        <v>233</v>
+        <v>106</v>
       </c>
       <c r="N34" t="s">
-        <v>844</v>
+        <v>740</v>
       </c>
       <c r="O34" t="s">
-        <v>100</v>
+        <v>424</v>
       </c>
       <c r="P34" t="s">
         <v>262</v>
       </c>
       <c r="Q34" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="R34" t="s">
-        <v>152</v>
+        <v>183</v>
       </c>
       <c r="S34" t="s">
         <v>236</v>
       </c>
       <c r="T34" s="2">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="U34" t="s">
         <v>105</v>
@@ -13180,25 +13180,25 @@
         <v>106</v>
       </c>
       <c r="X34" t="s">
+        <v>209</v>
+      </c>
+      <c r="Y34" t="s">
+        <v>184</v>
+      </c>
+      <c r="Z34" t="s">
         <v>107</v>
       </c>
-      <c r="Y34" t="s">
-        <v>107</v>
-      </c>
-      <c r="Z34" t="s">
-        <v>209</v>
-      </c>
       <c r="AA34" t="s">
-        <v>447</v>
+        <v>108</v>
       </c>
       <c r="AB34" t="s">
-        <v>845</v>
+        <v>741</v>
       </c>
       <c r="AC34" t="s">
+        <v>111</v>
+      </c>
+      <c r="AD34" t="s">
         <v>154</v>
-      </c>
-      <c r="AD34" t="s">
-        <v>111</v>
       </c>
       <c r="AE34" t="s">
         <v>110</v>
@@ -13207,7 +13207,7 @@
         <v>111</v>
       </c>
       <c r="AG34" t="s">
-        <v>154</v>
+        <v>110</v>
       </c>
       <c r="AH34" t="s">
         <v>106</v>
@@ -13216,10 +13216,10 @@
         <v>106</v>
       </c>
       <c r="AJ34" t="s">
-        <v>354</v>
+        <v>658</v>
       </c>
       <c r="AK34" t="s">
-        <v>113</v>
+        <v>187</v>
       </c>
       <c r="AL34" t="s">
         <v>114</v>
@@ -13228,40 +13228,40 @@
         <v>114</v>
       </c>
       <c r="AN34" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="AO34" t="s">
-        <v>115</v>
+        <v>265</v>
       </c>
       <c r="AP34" t="s">
-        <v>212</v>
+        <v>309</v>
       </c>
       <c r="AQ34" t="s">
-        <v>159</v>
+        <v>114</v>
       </c>
       <c r="AR34" t="s">
-        <v>106</v>
+        <v>742</v>
       </c>
       <c r="AS34" t="s">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="AT34" t="s">
         <v>106</v>
       </c>
       <c r="AU34" t="s">
-        <v>846</v>
+        <v>743</v>
       </c>
       <c r="AV34" t="s">
-        <v>164</v>
+        <v>120</v>
       </c>
       <c r="AW34" t="s">
-        <v>847</v>
+        <v>744</v>
       </c>
       <c r="AX34" t="s">
-        <v>848</v>
+        <v>745</v>
       </c>
       <c r="AY34" t="s">
-        <v>849</v>
+        <v>746</v>
       </c>
       <c r="AZ34" t="s">
         <v>120</v>
@@ -13285,46 +13285,46 @@
         <v>125</v>
       </c>
       <c r="BG34" t="s">
-        <v>850</v>
+        <v>747</v>
       </c>
       <c r="BH34" t="s">
-        <v>851</v>
+        <v>748</v>
       </c>
       <c r="BI34" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="BJ34" t="s">
-        <v>852</v>
+        <v>749</v>
       </c>
       <c r="BK34" t="s">
-        <v>167</v>
+        <v>130</v>
       </c>
       <c r="BL34" t="s">
-        <v>853</v>
+        <v>750</v>
       </c>
       <c r="BM34" t="s">
         <v>128</v>
       </c>
       <c r="BN34" t="s">
-        <v>854</v>
+        <v>751</v>
       </c>
       <c r="BO34" t="s">
-        <v>167</v>
+        <v>128</v>
       </c>
       <c r="BP34" t="s">
-        <v>855</v>
+        <v>752</v>
       </c>
       <c r="BQ34" t="s">
+        <v>128</v>
+      </c>
+      <c r="BR34" t="s">
+        <v>753</v>
+      </c>
+      <c r="BS34" t="s">
         <v>130</v>
       </c>
-      <c r="BR34" t="s">
-        <v>856</v>
-      </c>
-      <c r="BS34" t="s">
-        <v>128</v>
-      </c>
       <c r="BT34" t="s">
-        <v>857</v>
+        <v>754</v>
       </c>
       <c r="BU34" t="s">
         <v>128</v>
@@ -13339,45 +13339,45 @@
         <v>138</v>
       </c>
       <c r="BY34" t="s">
-        <v>858</v>
+        <v>755</v>
       </c>
       <c r="BZ34" t="s">
-        <v>859</v>
+        <v>756</v>
       </c>
       <c r="CA34" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="CB34" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="CC34" t="s">
         <v>102</v>
       </c>
       <c r="CD34" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="CE34" t="s">
         <v>114</v>
       </c>
       <c r="CF34" t="s">
-        <v>140</v>
+        <v>227</v>
       </c>
       <c r="CG34" t="s">
-        <v>860</v>
+        <v>757</v>
       </c>
       <c r="CH34" t="s">
         <v>142</v>
       </c>
       <c r="CJ34" t="s">
-        <v>177</v>
+        <v>144</v>
       </c>
     </row>
-    <row r="35" spans="1:88">
+    <row r="35" spans="1:88" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>88</v>
       </c>
       <c r="B35" s="1">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="C35" t="s">
         <v>145</v>
@@ -13389,16 +13389,16 @@
         <v>91</v>
       </c>
       <c r="F35" t="s">
-        <v>861</v>
+        <v>758</v>
       </c>
       <c r="G35" t="s">
-        <v>862</v>
+        <v>759</v>
       </c>
       <c r="H35" t="s">
         <v>94</v>
       </c>
       <c r="I35" s="1">
-        <v>36267</v>
+        <v>35779</v>
       </c>
       <c r="J35" t="s">
         <v>95</v>
@@ -13413,7 +13413,7 @@
         <v>106</v>
       </c>
       <c r="N35" t="s">
-        <v>863</v>
+        <v>760</v>
       </c>
       <c r="O35" t="s">
         <v>182</v>
@@ -13428,10 +13428,10 @@
         <v>152</v>
       </c>
       <c r="S35" t="s">
-        <v>208</v>
+        <v>236</v>
       </c>
       <c r="T35" s="2">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="U35" t="s">
         <v>105</v>
@@ -13443,7 +13443,7 @@
         <v>106</v>
       </c>
       <c r="X35" t="s">
-        <v>184</v>
+        <v>209</v>
       </c>
       <c r="Y35" t="s">
         <v>107</v>
@@ -13455,19 +13455,19 @@
         <v>447</v>
       </c>
       <c r="AB35" t="s">
-        <v>864</v>
+        <v>761</v>
       </c>
       <c r="AC35" t="s">
         <v>154</v>
       </c>
       <c r="AD35" t="s">
-        <v>154</v>
+        <v>110</v>
       </c>
       <c r="AE35" t="s">
         <v>110</v>
       </c>
       <c r="AF35" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AG35" t="s">
         <v>110</v>
@@ -13479,25 +13479,25 @@
         <v>106</v>
       </c>
       <c r="AJ35" t="s">
-        <v>865</v>
+        <v>762</v>
       </c>
       <c r="AK35" t="s">
-        <v>156</v>
+        <v>187</v>
       </c>
       <c r="AL35" t="s">
         <v>114</v>
       </c>
       <c r="AM35" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="AN35" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="AO35" t="s">
         <v>157</v>
       </c>
       <c r="AP35" t="s">
-        <v>212</v>
+        <v>116</v>
       </c>
       <c r="AQ35" t="s">
         <v>159</v>
@@ -13512,22 +13512,22 @@
         <v>106</v>
       </c>
       <c r="AU35" t="s">
-        <v>866</v>
+        <v>763</v>
       </c>
       <c r="AV35" t="s">
-        <v>164</v>
+        <v>764</v>
       </c>
       <c r="AW35" t="s">
-        <v>867</v>
+        <v>765</v>
       </c>
       <c r="AX35" t="s">
-        <v>868</v>
+        <v>766</v>
       </c>
       <c r="AY35" t="s">
-        <v>869</v>
+        <v>767</v>
       </c>
       <c r="AZ35" t="s">
-        <v>164</v>
+        <v>768</v>
       </c>
       <c r="BA35" t="s">
         <v>114</v>
@@ -13539,73 +13539,73 @@
         <v>114</v>
       </c>
       <c r="BD35" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="BE35" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="BF35" t="s">
         <v>125</v>
       </c>
       <c r="BG35" t="s">
-        <v>870</v>
+        <v>769</v>
       </c>
       <c r="BH35" t="s">
-        <v>871</v>
+        <v>770</v>
       </c>
       <c r="BI35" t="s">
-        <v>128</v>
+        <v>167</v>
       </c>
       <c r="BJ35" t="s">
-        <v>872</v>
+        <v>771</v>
       </c>
       <c r="BK35" t="s">
-        <v>128</v>
+        <v>167</v>
       </c>
       <c r="BL35" t="s">
-        <v>873</v>
+        <v>772</v>
       </c>
       <c r="BM35" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="BN35" t="s">
-        <v>874</v>
+        <v>773</v>
       </c>
       <c r="BO35" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="BP35" t="s">
-        <v>875</v>
+        <v>774</v>
       </c>
       <c r="BQ35" t="s">
         <v>128</v>
       </c>
       <c r="BR35" t="s">
-        <v>876</v>
+        <v>775</v>
       </c>
       <c r="BS35" t="s">
-        <v>128</v>
+        <v>167</v>
       </c>
       <c r="BT35" t="s">
-        <v>877</v>
+        <v>776</v>
       </c>
       <c r="BU35" t="s">
-        <v>167</v>
+        <v>130</v>
       </c>
       <c r="BV35" t="s">
-        <v>136</v>
+        <v>200</v>
       </c>
       <c r="BW35" t="s">
-        <v>137</v>
+        <v>200</v>
       </c>
       <c r="BX35" t="s">
-        <v>138</v>
+        <v>777</v>
       </c>
       <c r="BY35" t="s">
-        <v>878</v>
+        <v>778</v>
       </c>
       <c r="BZ35" t="s">
-        <v>879</v>
+        <v>779</v>
       </c>
       <c r="CA35" t="s">
         <v>102</v>
@@ -13617,7 +13617,7 @@
         <v>102</v>
       </c>
       <c r="CD35" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="CE35" t="s">
         <v>114</v>
@@ -13626,7 +13626,7 @@
         <v>140</v>
       </c>
       <c r="CG35" t="s">
-        <v>880</v>
+        <v>780</v>
       </c>
       <c r="CH35" t="s">
         <v>142</v>
@@ -13635,7 +13635,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="36" spans="1:88">
+    <row r="36" spans="1:88" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>88</v>
       </c>
@@ -13643,7 +13643,7 @@
         <v>46162</v>
       </c>
       <c r="C36" t="s">
-        <v>89</v>
+        <v>280</v>
       </c>
       <c r="D36" t="s">
         <v>90</v>
@@ -13652,16 +13652,16 @@
         <v>91</v>
       </c>
       <c r="F36" t="s">
-        <v>881</v>
+        <v>820</v>
       </c>
       <c r="G36" t="s">
-        <v>882</v>
+        <v>821</v>
       </c>
       <c r="H36" t="s">
         <v>94</v>
       </c>
       <c r="I36" s="1">
-        <v>33104</v>
+        <v>34741</v>
       </c>
       <c r="J36" t="s">
         <v>95</v>
@@ -13670,16 +13670,16 @@
         <v>96</v>
       </c>
       <c r="L36" t="s">
-        <v>97</v>
+        <v>822</v>
       </c>
       <c r="M36" t="s">
-        <v>883</v>
+        <v>106</v>
       </c>
       <c r="N36" t="s">
-        <v>884</v>
+        <v>823</v>
       </c>
       <c r="O36" t="s">
-        <v>593</v>
+        <v>100</v>
       </c>
       <c r="P36" t="s">
         <v>262</v>
@@ -13688,13 +13688,13 @@
         <v>102</v>
       </c>
       <c r="R36" t="s">
-        <v>352</v>
+        <v>183</v>
       </c>
       <c r="S36" t="s">
-        <v>236</v>
+        <v>104</v>
       </c>
       <c r="T36" s="2">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="U36" t="s">
         <v>105</v>
@@ -13706,31 +13706,31 @@
         <v>106</v>
       </c>
       <c r="X36" t="s">
-        <v>209</v>
+        <v>107</v>
       </c>
       <c r="Y36" t="s">
         <v>107</v>
       </c>
       <c r="Z36" t="s">
-        <v>107</v>
+        <v>184</v>
       </c>
       <c r="AA36" t="s">
-        <v>447</v>
+        <v>108</v>
       </c>
       <c r="AB36" t="s">
-        <v>885</v>
+        <v>824</v>
       </c>
       <c r="AC36" t="s">
+        <v>110</v>
+      </c>
+      <c r="AD36" t="s">
         <v>154</v>
-      </c>
-      <c r="AD36" t="s">
-        <v>111</v>
       </c>
       <c r="AE36" t="s">
         <v>154</v>
       </c>
       <c r="AF36" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="AG36" t="s">
         <v>110</v>
@@ -13742,22 +13742,22 @@
         <v>106</v>
       </c>
       <c r="AJ36" t="s">
-        <v>886</v>
+        <v>825</v>
       </c>
       <c r="AK36" t="s">
-        <v>239</v>
+        <v>113</v>
       </c>
       <c r="AL36" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="AM36" t="s">
         <v>102</v>
       </c>
       <c r="AN36" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="AO36" t="s">
-        <v>157</v>
+        <v>265</v>
       </c>
       <c r="AP36" t="s">
         <v>116</v>
@@ -13766,7 +13766,7 @@
         <v>114</v>
       </c>
       <c r="AR36" t="s">
-        <v>887</v>
+        <v>826</v>
       </c>
       <c r="AS36" t="s">
         <v>118</v>
@@ -13775,22 +13775,22 @@
         <v>106</v>
       </c>
       <c r="AU36" t="s">
-        <v>888</v>
+        <v>827</v>
       </c>
       <c r="AV36" t="s">
-        <v>106</v>
+        <v>684</v>
       </c>
       <c r="AW36" t="s">
-        <v>889</v>
+        <v>828</v>
       </c>
       <c r="AX36" t="s">
-        <v>890</v>
+        <v>829</v>
       </c>
       <c r="AY36" t="s">
-        <v>891</v>
+        <v>830</v>
       </c>
       <c r="AZ36" t="s">
-        <v>120</v>
+        <v>831</v>
       </c>
       <c r="BA36" t="s">
         <v>114</v>
@@ -13802,55 +13802,55 @@
         <v>114</v>
       </c>
       <c r="BD36" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="BE36" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="BF36" t="s">
         <v>125</v>
       </c>
       <c r="BG36" t="s">
-        <v>106</v>
+        <v>832</v>
       </c>
       <c r="BH36" t="s">
-        <v>106</v>
+        <v>833</v>
       </c>
       <c r="BI36" t="s">
-        <v>167</v>
+        <v>128</v>
       </c>
       <c r="BJ36" t="s">
-        <v>106</v>
+        <v>834</v>
       </c>
       <c r="BK36" t="s">
-        <v>167</v>
+        <v>128</v>
       </c>
       <c r="BL36" t="s">
-        <v>892</v>
+        <v>835</v>
       </c>
       <c r="BM36" t="s">
         <v>128</v>
       </c>
       <c r="BN36" t="s">
-        <v>893</v>
+        <v>836</v>
       </c>
       <c r="BO36" t="s">
         <v>128</v>
       </c>
       <c r="BP36" t="s">
-        <v>894</v>
+        <v>837</v>
       </c>
       <c r="BQ36" t="s">
         <v>128</v>
       </c>
       <c r="BR36" t="s">
-        <v>895</v>
+        <v>838</v>
       </c>
       <c r="BS36" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="BT36" t="s">
-        <v>896</v>
+        <v>839</v>
       </c>
       <c r="BU36" t="s">
         <v>128</v>
@@ -13865,16 +13865,16 @@
         <v>138</v>
       </c>
       <c r="BY36" t="s">
-        <v>897</v>
+        <v>832</v>
       </c>
       <c r="BZ36" t="s">
-        <v>898</v>
+        <v>840</v>
       </c>
       <c r="CA36" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="CB36" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="CC36" t="s">
         <v>102</v>
@@ -13883,13 +13883,13 @@
         <v>102</v>
       </c>
       <c r="CE36" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="CF36" t="s">
-        <v>227</v>
+        <v>140</v>
       </c>
       <c r="CG36" t="s">
-        <v>106</v>
+        <v>841</v>
       </c>
       <c r="CH36" t="s">
         <v>142</v>
@@ -13898,7 +13898,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="37" spans="1:88">
+    <row r="37" spans="1:88" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>88</v>
       </c>
@@ -14162,7 +14162,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="38" spans="1:88">
+    <row r="38" spans="1:88" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>88</v>
       </c>
@@ -14170,7 +14170,7 @@
         <v>46162</v>
       </c>
       <c r="C38" t="s">
-        <v>347</v>
+        <v>145</v>
       </c>
       <c r="D38" t="s">
         <v>90</v>
@@ -14179,16 +14179,16 @@
         <v>91</v>
       </c>
       <c r="F38" t="s">
-        <v>918</v>
+        <v>842</v>
       </c>
       <c r="G38" t="s">
-        <v>919</v>
+        <v>843</v>
       </c>
       <c r="H38" t="s">
         <v>94</v>
       </c>
       <c r="I38" s="1">
-        <v>36447</v>
+        <v>35687</v>
       </c>
       <c r="J38" t="s">
         <v>95</v>
@@ -14197,31 +14197,31 @@
         <v>96</v>
       </c>
       <c r="L38" t="s">
-        <v>920</v>
+        <v>97</v>
       </c>
       <c r="M38" t="s">
-        <v>106</v>
+        <v>233</v>
       </c>
       <c r="N38" t="s">
-        <v>921</v>
+        <v>844</v>
       </c>
       <c r="O38" t="s">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="P38" t="s">
-        <v>101</v>
+        <v>262</v>
       </c>
       <c r="Q38" t="s">
         <v>102</v>
       </c>
       <c r="R38" t="s">
-        <v>922</v>
+        <v>152</v>
       </c>
       <c r="S38" t="s">
-        <v>104</v>
+        <v>236</v>
       </c>
       <c r="T38" s="2">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="U38" t="s">
         <v>105</v>
@@ -14233,35 +14233,35 @@
         <v>106</v>
       </c>
       <c r="X38" t="s">
-        <v>209</v>
+        <v>107</v>
       </c>
       <c r="Y38" t="s">
         <v>107</v>
       </c>
       <c r="Z38" t="s">
-        <v>107</v>
+        <v>209</v>
       </c>
       <c r="AA38" t="s">
-        <v>108</v>
+        <v>447</v>
       </c>
       <c r="AB38" t="s">
-        <v>923</v>
+        <v>845</v>
       </c>
       <c r="AC38" t="s">
         <v>154</v>
       </c>
       <c r="AD38" t="s">
+        <v>111</v>
+      </c>
+      <c r="AE38" t="s">
         <v>110</v>
       </c>
-      <c r="AE38" t="s">
+      <c r="AF38" t="s">
+        <v>111</v>
+      </c>
+      <c r="AG38" t="s">
         <v>154</v>
       </c>
-      <c r="AF38" t="s">
-        <v>110</v>
-      </c>
-      <c r="AG38" t="s">
-        <v>110</v>
-      </c>
       <c r="AH38" t="s">
         <v>106</v>
       </c>
@@ -14269,10 +14269,10 @@
         <v>106</v>
       </c>
       <c r="AJ38" t="s">
-        <v>924</v>
+        <v>354</v>
       </c>
       <c r="AK38" t="s">
-        <v>187</v>
+        <v>113</v>
       </c>
       <c r="AL38" t="s">
         <v>114</v>
@@ -14284,10 +14284,10 @@
         <v>114</v>
       </c>
       <c r="AO38" t="s">
-        <v>265</v>
+        <v>115</v>
       </c>
       <c r="AP38" t="s">
-        <v>309</v>
+        <v>212</v>
       </c>
       <c r="AQ38" t="s">
         <v>159</v>
@@ -14302,22 +14302,22 @@
         <v>106</v>
       </c>
       <c r="AU38" t="s">
-        <v>925</v>
+        <v>846</v>
       </c>
       <c r="AV38" t="s">
-        <v>926</v>
+        <v>164</v>
       </c>
       <c r="AW38" t="s">
-        <v>927</v>
+        <v>847</v>
       </c>
       <c r="AX38" t="s">
-        <v>928</v>
+        <v>848</v>
       </c>
       <c r="AY38" t="s">
-        <v>929</v>
+        <v>849</v>
       </c>
       <c r="AZ38" t="s">
-        <v>930</v>
+        <v>120</v>
       </c>
       <c r="BA38" t="s">
         <v>114</v>
@@ -14329,55 +14329,55 @@
         <v>114</v>
       </c>
       <c r="BD38" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="BE38" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="BF38" t="s">
         <v>125</v>
       </c>
       <c r="BG38" t="s">
-        <v>931</v>
+        <v>850</v>
       </c>
       <c r="BH38" t="s">
-        <v>932</v>
+        <v>851</v>
       </c>
       <c r="BI38" t="s">
         <v>128</v>
       </c>
       <c r="BJ38" t="s">
-        <v>933</v>
+        <v>852</v>
       </c>
       <c r="BK38" t="s">
-        <v>128</v>
+        <v>167</v>
       </c>
       <c r="BL38" t="s">
-        <v>934</v>
+        <v>853</v>
       </c>
       <c r="BM38" t="s">
         <v>128</v>
       </c>
       <c r="BN38" t="s">
-        <v>935</v>
+        <v>854</v>
       </c>
       <c r="BO38" t="s">
-        <v>128</v>
+        <v>167</v>
       </c>
       <c r="BP38" t="s">
-        <v>936</v>
+        <v>855</v>
       </c>
       <c r="BQ38" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="BR38" t="s">
-        <v>937</v>
+        <v>856</v>
       </c>
       <c r="BS38" t="s">
         <v>128</v>
       </c>
       <c r="BT38" t="s">
-        <v>938</v>
+        <v>857</v>
       </c>
       <c r="BU38" t="s">
         <v>128</v>
@@ -14392,31 +14392,31 @@
         <v>138</v>
       </c>
       <c r="BY38" t="s">
-        <v>939</v>
+        <v>858</v>
       </c>
       <c r="BZ38" t="s">
-        <v>940</v>
+        <v>859</v>
       </c>
       <c r="CA38" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="CB38" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="CC38" t="s">
         <v>102</v>
       </c>
       <c r="CD38" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="CE38" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="CF38" t="s">
-        <v>227</v>
+        <v>140</v>
       </c>
       <c r="CG38" t="s">
-        <v>941</v>
+        <v>860</v>
       </c>
       <c r="CH38" t="s">
         <v>142</v>
@@ -14425,7 +14425,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="39" spans="1:88">
+    <row r="39" spans="1:88" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>88</v>
       </c>
@@ -14689,7 +14689,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="40" spans="1:88">
+    <row r="40" spans="1:88" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>88</v>
       </c>
@@ -14955,7 +14955,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="41" spans="1:88">
+    <row r="41" spans="1:88" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>88</v>
       </c>
@@ -14963,7 +14963,7 @@
         <v>46162</v>
       </c>
       <c r="C41" t="s">
-        <v>347</v>
+        <v>145</v>
       </c>
       <c r="D41" t="s">
         <v>90</v>
@@ -14972,16 +14972,16 @@
         <v>91</v>
       </c>
       <c r="F41" t="s">
-        <v>980</v>
+        <v>861</v>
       </c>
       <c r="G41" t="s">
-        <v>981</v>
+        <v>862</v>
       </c>
       <c r="H41" t="s">
         <v>94</v>
       </c>
       <c r="I41" s="1">
-        <v>37716</v>
+        <v>36267</v>
       </c>
       <c r="J41" t="s">
         <v>95</v>
@@ -14990,31 +14990,31 @@
         <v>96</v>
       </c>
       <c r="L41" t="s">
-        <v>205</v>
+        <v>397</v>
       </c>
       <c r="M41" t="s">
         <v>106</v>
       </c>
       <c r="N41" t="s">
-        <v>982</v>
+        <v>863</v>
       </c>
       <c r="O41" t="s">
         <v>182</v>
       </c>
       <c r="P41" t="s">
-        <v>151</v>
+        <v>101</v>
       </c>
       <c r="Q41" t="s">
         <v>102</v>
       </c>
       <c r="R41" t="s">
-        <v>352</v>
+        <v>152</v>
       </c>
       <c r="S41" t="s">
         <v>208</v>
       </c>
       <c r="T41" s="2">
-        <v>3</v>
+        <v>50</v>
       </c>
       <c r="U41" t="s">
         <v>105</v>
@@ -15026,31 +15026,31 @@
         <v>106</v>
       </c>
       <c r="X41" t="s">
-        <v>107</v>
+        <v>184</v>
       </c>
       <c r="Y41" t="s">
         <v>107</v>
       </c>
       <c r="Z41" t="s">
-        <v>209</v>
+        <v>107</v>
       </c>
       <c r="AA41" t="s">
-        <v>108</v>
+        <v>447</v>
       </c>
       <c r="AB41" t="s">
-        <v>983</v>
+        <v>864</v>
       </c>
       <c r="AC41" t="s">
-        <v>111</v>
+        <v>154</v>
       </c>
       <c r="AD41" t="s">
-        <v>111</v>
+        <v>154</v>
       </c>
       <c r="AE41" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="AF41" t="s">
-        <v>154</v>
+        <v>110</v>
       </c>
       <c r="AG41" t="s">
         <v>110</v>
@@ -15062,10 +15062,10 @@
         <v>106</v>
       </c>
       <c r="AJ41" t="s">
-        <v>984</v>
+        <v>865</v>
       </c>
       <c r="AK41" t="s">
-        <v>239</v>
+        <v>156</v>
       </c>
       <c r="AL41" t="s">
         <v>114</v>
@@ -15074,13 +15074,13 @@
         <v>102</v>
       </c>
       <c r="AN41" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="AO41" t="s">
         <v>157</v>
       </c>
       <c r="AP41" t="s">
-        <v>158</v>
+        <v>212</v>
       </c>
       <c r="AQ41" t="s">
         <v>159</v>
@@ -15089,28 +15089,28 @@
         <v>106</v>
       </c>
       <c r="AS41" t="s">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="AT41" t="s">
         <v>106</v>
       </c>
       <c r="AU41" t="s">
-        <v>985</v>
+        <v>866</v>
       </c>
       <c r="AV41" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="AW41" t="s">
-        <v>986</v>
+        <v>867</v>
       </c>
       <c r="AX41" t="s">
-        <v>987</v>
+        <v>868</v>
       </c>
       <c r="AY41" t="s">
-        <v>988</v>
+        <v>869</v>
       </c>
       <c r="AZ41" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="BA41" t="s">
         <v>114</v>
@@ -15131,49 +15131,49 @@
         <v>125</v>
       </c>
       <c r="BG41" t="s">
-        <v>989</v>
+        <v>870</v>
       </c>
       <c r="BH41" t="s">
-        <v>990</v>
+        <v>871</v>
       </c>
       <c r="BI41" t="s">
+        <v>128</v>
+      </c>
+      <c r="BJ41" t="s">
+        <v>872</v>
+      </c>
+      <c r="BK41" t="s">
+        <v>128</v>
+      </c>
+      <c r="BL41" t="s">
+        <v>873</v>
+      </c>
+      <c r="BM41" t="s">
+        <v>128</v>
+      </c>
+      <c r="BN41" t="s">
+        <v>874</v>
+      </c>
+      <c r="BO41" t="s">
+        <v>128</v>
+      </c>
+      <c r="BP41" t="s">
+        <v>875</v>
+      </c>
+      <c r="BQ41" t="s">
+        <v>128</v>
+      </c>
+      <c r="BR41" t="s">
+        <v>876</v>
+      </c>
+      <c r="BS41" t="s">
+        <v>128</v>
+      </c>
+      <c r="BT41" t="s">
+        <v>877</v>
+      </c>
+      <c r="BU41" t="s">
         <v>167</v>
-      </c>
-      <c r="BJ41" t="s">
-        <v>991</v>
-      </c>
-      <c r="BK41" t="s">
-        <v>128</v>
-      </c>
-      <c r="BL41" t="s">
-        <v>992</v>
-      </c>
-      <c r="BM41" t="s">
-        <v>128</v>
-      </c>
-      <c r="BN41" t="s">
-        <v>993</v>
-      </c>
-      <c r="BO41" t="s">
-        <v>128</v>
-      </c>
-      <c r="BP41" t="s">
-        <v>994</v>
-      </c>
-      <c r="BQ41" t="s">
-        <v>128</v>
-      </c>
-      <c r="BR41" t="s">
-        <v>995</v>
-      </c>
-      <c r="BS41" t="s">
-        <v>128</v>
-      </c>
-      <c r="BT41" t="s">
-        <v>996</v>
-      </c>
-      <c r="BU41" t="s">
-        <v>128</v>
       </c>
       <c r="BV41" t="s">
         <v>136</v>
@@ -15185,10 +15185,10 @@
         <v>138</v>
       </c>
       <c r="BY41" t="s">
-        <v>997</v>
+        <v>878</v>
       </c>
       <c r="BZ41" t="s">
-        <v>998</v>
+        <v>879</v>
       </c>
       <c r="CA41" t="s">
         <v>102</v>
@@ -15209,16 +15209,16 @@
         <v>140</v>
       </c>
       <c r="CG41" t="s">
-        <v>999</v>
+        <v>880</v>
       </c>
       <c r="CH41" t="s">
-        <v>257</v>
+        <v>142</v>
       </c>
       <c r="CJ41" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="42" spans="1:88">
+    <row r="42" spans="1:88" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>88</v>
       </c>
@@ -15226,7 +15226,7 @@
         <v>46162</v>
       </c>
       <c r="C42" t="s">
-        <v>145</v>
+        <v>89</v>
       </c>
       <c r="D42" t="s">
         <v>90</v>
@@ -15235,16 +15235,16 @@
         <v>91</v>
       </c>
       <c r="F42" t="s">
-        <v>1000</v>
+        <v>881</v>
       </c>
       <c r="G42" t="s">
-        <v>1001</v>
+        <v>882</v>
       </c>
       <c r="H42" t="s">
         <v>94</v>
       </c>
       <c r="I42" s="1">
-        <v>38586</v>
+        <v>33104</v>
       </c>
       <c r="J42" t="s">
         <v>95</v>
@@ -15253,31 +15253,31 @@
         <v>96</v>
       </c>
       <c r="L42" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="M42" t="s">
-        <v>1002</v>
+        <v>883</v>
       </c>
       <c r="N42" t="s">
-        <v>206</v>
+        <v>884</v>
       </c>
       <c r="O42" t="s">
-        <v>150</v>
+        <v>593</v>
       </c>
       <c r="P42" t="s">
-        <v>101</v>
+        <v>262</v>
       </c>
       <c r="Q42" t="s">
         <v>102</v>
       </c>
       <c r="R42" t="s">
-        <v>152</v>
+        <v>352</v>
       </c>
       <c r="S42" t="s">
         <v>236</v>
       </c>
       <c r="T42" s="2">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="U42" t="s">
         <v>105</v>
@@ -15289,7 +15289,7 @@
         <v>106</v>
       </c>
       <c r="X42" t="s">
-        <v>107</v>
+        <v>209</v>
       </c>
       <c r="Y42" t="s">
         <v>107</v>
@@ -15298,10 +15298,10 @@
         <v>107</v>
       </c>
       <c r="AA42" t="s">
-        <v>263</v>
+        <v>447</v>
       </c>
       <c r="AB42" t="s">
-        <v>106</v>
+        <v>885</v>
       </c>
       <c r="AC42" t="s">
         <v>154</v>
@@ -15310,7 +15310,7 @@
         <v>111</v>
       </c>
       <c r="AE42" t="s">
-        <v>111</v>
+        <v>154</v>
       </c>
       <c r="AF42" t="s">
         <v>111</v>
@@ -15325,10 +15325,10 @@
         <v>106</v>
       </c>
       <c r="AJ42" t="s">
-        <v>1003</v>
+        <v>886</v>
       </c>
       <c r="AK42" t="s">
-        <v>187</v>
+        <v>239</v>
       </c>
       <c r="AL42" t="s">
         <v>102</v>
@@ -15337,43 +15337,43 @@
         <v>102</v>
       </c>
       <c r="AN42" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="AO42" t="s">
         <v>157</v>
       </c>
       <c r="AP42" t="s">
-        <v>158</v>
+        <v>116</v>
       </c>
       <c r="AQ42" t="s">
-        <v>159</v>
+        <v>114</v>
       </c>
       <c r="AR42" t="s">
-        <v>106</v>
+        <v>887</v>
       </c>
       <c r="AS42" t="s">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="AT42" t="s">
         <v>106</v>
       </c>
       <c r="AU42" t="s">
-        <v>1004</v>
+        <v>888</v>
       </c>
       <c r="AV42" t="s">
-        <v>164</v>
+        <v>106</v>
       </c>
       <c r="AW42" t="s">
-        <v>1005</v>
+        <v>889</v>
       </c>
       <c r="AX42" t="s">
-        <v>1006</v>
+        <v>890</v>
       </c>
       <c r="AY42" t="s">
-        <v>1007</v>
+        <v>891</v>
       </c>
       <c r="AZ42" t="s">
-        <v>164</v>
+        <v>120</v>
       </c>
       <c r="BA42" t="s">
         <v>114</v>
@@ -15394,46 +15394,46 @@
         <v>125</v>
       </c>
       <c r="BG42" t="s">
-        <v>1008</v>
+        <v>106</v>
       </c>
       <c r="BH42" t="s">
-        <v>1009</v>
+        <v>106</v>
       </c>
       <c r="BI42" t="s">
-        <v>128</v>
+        <v>167</v>
       </c>
       <c r="BJ42" t="s">
-        <v>1010</v>
+        <v>106</v>
       </c>
       <c r="BK42" t="s">
-        <v>128</v>
+        <v>167</v>
       </c>
       <c r="BL42" t="s">
-        <v>1011</v>
+        <v>892</v>
       </c>
       <c r="BM42" t="s">
         <v>128</v>
       </c>
       <c r="BN42" t="s">
-        <v>1012</v>
+        <v>893</v>
       </c>
       <c r="BO42" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="BP42" t="s">
-        <v>1013</v>
+        <v>894</v>
       </c>
       <c r="BQ42" t="s">
         <v>128</v>
       </c>
       <c r="BR42" t="s">
-        <v>1014</v>
+        <v>895</v>
       </c>
       <c r="BS42" t="s">
-        <v>167</v>
+        <v>128</v>
       </c>
       <c r="BT42" t="s">
-        <v>1015</v>
+        <v>896</v>
       </c>
       <c r="BU42" t="s">
         <v>128</v>
@@ -15448,13 +15448,13 @@
         <v>138</v>
       </c>
       <c r="BY42" t="s">
-        <v>1016</v>
+        <v>897</v>
       </c>
       <c r="BZ42" t="s">
-        <v>1017</v>
+        <v>898</v>
       </c>
       <c r="CA42" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="CB42" t="s">
         <v>102</v>
@@ -15463,16 +15463,16 @@
         <v>102</v>
       </c>
       <c r="CD42" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="CE42" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="CF42" t="s">
-        <v>140</v>
+        <v>227</v>
       </c>
       <c r="CG42" t="s">
-        <v>1018</v>
+        <v>106</v>
       </c>
       <c r="CH42" t="s">
         <v>142</v>
@@ -15481,7 +15481,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="43" spans="1:88">
+    <row r="43" spans="1:88" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>88</v>
       </c>
@@ -15489,7 +15489,7 @@
         <v>46162</v>
       </c>
       <c r="C43" t="s">
-        <v>145</v>
+        <v>347</v>
       </c>
       <c r="D43" t="s">
         <v>90</v>
@@ -15498,16 +15498,16 @@
         <v>91</v>
       </c>
       <c r="F43" t="s">
-        <v>1019</v>
+        <v>918</v>
       </c>
       <c r="G43" t="s">
-        <v>1020</v>
+        <v>919</v>
       </c>
       <c r="H43" t="s">
         <v>94</v>
       </c>
       <c r="I43" s="1">
-        <v>37292</v>
+        <v>36447</v>
       </c>
       <c r="J43" t="s">
         <v>95</v>
@@ -15516,16 +15516,16 @@
         <v>96</v>
       </c>
       <c r="L43" t="s">
-        <v>148</v>
+        <v>920</v>
       </c>
       <c r="M43" t="s">
         <v>106</v>
       </c>
       <c r="N43" t="s">
-        <v>1021</v>
+        <v>921</v>
       </c>
       <c r="O43" t="s">
-        <v>593</v>
+        <v>150</v>
       </c>
       <c r="P43" t="s">
         <v>101</v>
@@ -15534,13 +15534,13 @@
         <v>102</v>
       </c>
       <c r="R43" t="s">
-        <v>152</v>
+        <v>922</v>
       </c>
       <c r="S43" t="s">
-        <v>208</v>
+        <v>104</v>
       </c>
       <c r="T43" s="2">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="U43" t="s">
         <v>105</v>
@@ -15552,25 +15552,25 @@
         <v>106</v>
       </c>
       <c r="X43" t="s">
-        <v>107</v>
+        <v>209</v>
       </c>
       <c r="Y43" t="s">
         <v>107</v>
       </c>
       <c r="Z43" t="s">
-        <v>209</v>
+        <v>107</v>
       </c>
       <c r="AA43" t="s">
         <v>108</v>
       </c>
       <c r="AB43" t="s">
-        <v>1022</v>
+        <v>923</v>
       </c>
       <c r="AC43" t="s">
-        <v>111</v>
+        <v>154</v>
       </c>
       <c r="AD43" t="s">
-        <v>154</v>
+        <v>110</v>
       </c>
       <c r="AE43" t="s">
         <v>154</v>
@@ -15588,10 +15588,10 @@
         <v>106</v>
       </c>
       <c r="AJ43" t="s">
-        <v>1023</v>
+        <v>924</v>
       </c>
       <c r="AK43" t="s">
-        <v>113</v>
+        <v>187</v>
       </c>
       <c r="AL43" t="s">
         <v>114</v>
@@ -15603,10 +15603,10 @@
         <v>114</v>
       </c>
       <c r="AO43" t="s">
-        <v>115</v>
+        <v>265</v>
       </c>
       <c r="AP43" t="s">
-        <v>116</v>
+        <v>309</v>
       </c>
       <c r="AQ43" t="s">
         <v>159</v>
@@ -15615,28 +15615,28 @@
         <v>106</v>
       </c>
       <c r="AS43" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="AT43" t="s">
         <v>106</v>
       </c>
       <c r="AU43" t="s">
-        <v>1024</v>
+        <v>925</v>
       </c>
       <c r="AV43" t="s">
-        <v>164</v>
+        <v>926</v>
       </c>
       <c r="AW43" t="s">
-        <v>1025</v>
+        <v>927</v>
       </c>
       <c r="AX43" t="s">
-        <v>1026</v>
+        <v>928</v>
       </c>
       <c r="AY43" t="s">
-        <v>1027</v>
+        <v>929</v>
       </c>
       <c r="AZ43" t="s">
-        <v>164</v>
+        <v>930</v>
       </c>
       <c r="BA43" t="s">
         <v>114</v>
@@ -15648,55 +15648,55 @@
         <v>114</v>
       </c>
       <c r="BD43" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="BE43" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="BF43" t="s">
         <v>125</v>
       </c>
       <c r="BG43" t="s">
-        <v>1028</v>
+        <v>931</v>
       </c>
       <c r="BH43" t="s">
-        <v>1029</v>
+        <v>932</v>
       </c>
       <c r="BI43" t="s">
         <v>128</v>
       </c>
       <c r="BJ43" t="s">
-        <v>1030</v>
+        <v>933</v>
       </c>
       <c r="BK43" t="s">
         <v>128</v>
       </c>
       <c r="BL43" t="s">
-        <v>1031</v>
+        <v>934</v>
       </c>
       <c r="BM43" t="s">
         <v>128</v>
       </c>
       <c r="BN43" t="s">
-        <v>1032</v>
+        <v>935</v>
       </c>
       <c r="BO43" t="s">
         <v>128</v>
       </c>
       <c r="BP43" t="s">
-        <v>1033</v>
+        <v>936</v>
       </c>
       <c r="BQ43" t="s">
         <v>128</v>
       </c>
       <c r="BR43" t="s">
-        <v>1034</v>
+        <v>937</v>
       </c>
       <c r="BS43" t="s">
         <v>128</v>
       </c>
       <c r="BT43" t="s">
-        <v>1035</v>
+        <v>938</v>
       </c>
       <c r="BU43" t="s">
         <v>128</v>
@@ -15711,31 +15711,31 @@
         <v>138</v>
       </c>
       <c r="BY43" t="s">
-        <v>1036</v>
+        <v>939</v>
       </c>
       <c r="BZ43" t="s">
-        <v>1037</v>
+        <v>940</v>
       </c>
       <c r="CA43" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="CB43" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="CC43" t="s">
         <v>102</v>
       </c>
       <c r="CD43" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="CE43" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="CF43" t="s">
-        <v>140</v>
+        <v>227</v>
       </c>
       <c r="CG43" t="s">
-        <v>1038</v>
+        <v>941</v>
       </c>
       <c r="CH43" t="s">
         <v>142</v>
@@ -15744,15 +15744,15 @@
         <v>177</v>
       </c>
     </row>
-    <row r="44" spans="1:88">
+    <row r="44" spans="1:88" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>88</v>
       </c>
       <c r="B44" s="1">
-        <v>46163</v>
+        <v>46162</v>
       </c>
       <c r="C44" t="s">
-        <v>145</v>
+        <v>347</v>
       </c>
       <c r="D44" t="s">
         <v>90</v>
@@ -15761,16 +15761,16 @@
         <v>91</v>
       </c>
       <c r="F44" t="s">
-        <v>1039</v>
+        <v>980</v>
       </c>
       <c r="G44" t="s">
-        <v>1040</v>
+        <v>981</v>
       </c>
       <c r="H44" t="s">
         <v>94</v>
       </c>
       <c r="I44" s="1">
-        <v>38355</v>
+        <v>37716</v>
       </c>
       <c r="J44" t="s">
         <v>95</v>
@@ -15779,31 +15779,31 @@
         <v>96</v>
       </c>
       <c r="L44" t="s">
-        <v>444</v>
+        <v>205</v>
       </c>
       <c r="M44" t="s">
         <v>106</v>
       </c>
       <c r="N44" t="s">
-        <v>1041</v>
+        <v>982</v>
       </c>
       <c r="O44" t="s">
         <v>182</v>
       </c>
       <c r="P44" t="s">
-        <v>262</v>
+        <v>151</v>
       </c>
       <c r="Q44" t="s">
         <v>102</v>
       </c>
       <c r="R44" t="s">
-        <v>152</v>
+        <v>352</v>
       </c>
       <c r="S44" t="s">
         <v>208</v>
       </c>
       <c r="T44" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="U44" t="s">
         <v>105</v>
@@ -15815,19 +15815,19 @@
         <v>106</v>
       </c>
       <c r="X44" t="s">
-        <v>209</v>
+        <v>107</v>
       </c>
       <c r="Y44" t="s">
         <v>107</v>
       </c>
       <c r="Z44" t="s">
-        <v>107</v>
+        <v>209</v>
       </c>
       <c r="AA44" t="s">
-        <v>263</v>
+        <v>108</v>
       </c>
       <c r="AB44" t="s">
-        <v>106</v>
+        <v>983</v>
       </c>
       <c r="AC44" t="s">
         <v>111</v>
@@ -15839,7 +15839,7 @@
         <v>111</v>
       </c>
       <c r="AF44" t="s">
-        <v>111</v>
+        <v>154</v>
       </c>
       <c r="AG44" t="s">
         <v>110</v>
@@ -15851,22 +15851,22 @@
         <v>106</v>
       </c>
       <c r="AJ44" t="s">
-        <v>553</v>
+        <v>984</v>
       </c>
       <c r="AK44" t="s">
-        <v>156</v>
+        <v>239</v>
       </c>
       <c r="AL44" t="s">
         <v>114</v>
       </c>
       <c r="AM44" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="AN44" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="AO44" t="s">
-        <v>115</v>
+        <v>157</v>
       </c>
       <c r="AP44" t="s">
         <v>158</v>
@@ -15878,28 +15878,28 @@
         <v>106</v>
       </c>
       <c r="AS44" t="s">
-        <v>1042</v>
+        <v>106</v>
       </c>
       <c r="AT44" t="s">
         <v>106</v>
       </c>
       <c r="AU44" t="s">
-        <v>1043</v>
+        <v>985</v>
       </c>
       <c r="AV44" t="s">
-        <v>164</v>
+        <v>120</v>
       </c>
       <c r="AW44" t="s">
-        <v>1044</v>
+        <v>986</v>
       </c>
       <c r="AX44" t="s">
-        <v>1045</v>
+        <v>987</v>
       </c>
       <c r="AY44" t="s">
-        <v>1046</v>
+        <v>988</v>
       </c>
       <c r="AZ44" t="s">
-        <v>164</v>
+        <v>120</v>
       </c>
       <c r="BA44" t="s">
         <v>114</v>
@@ -15908,7 +15908,7 @@
         <v>114</v>
       </c>
       <c r="BC44" t="s">
-        <v>246</v>
+        <v>114</v>
       </c>
       <c r="BD44" t="s">
         <v>102</v>
@@ -15920,49 +15920,49 @@
         <v>125</v>
       </c>
       <c r="BG44" t="s">
-        <v>1047</v>
+        <v>989</v>
       </c>
       <c r="BH44" t="s">
-        <v>1048</v>
+        <v>990</v>
       </c>
       <c r="BI44" t="s">
-        <v>128</v>
+        <v>167</v>
       </c>
       <c r="BJ44" t="s">
-        <v>1049</v>
+        <v>991</v>
       </c>
       <c r="BK44" t="s">
         <v>128</v>
       </c>
       <c r="BL44" t="s">
-        <v>1050</v>
+        <v>992</v>
       </c>
       <c r="BM44" t="s">
         <v>128</v>
       </c>
       <c r="BN44" t="s">
-        <v>1051</v>
+        <v>993</v>
       </c>
       <c r="BO44" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="BP44" t="s">
-        <v>1052</v>
+        <v>994</v>
       </c>
       <c r="BQ44" t="s">
         <v>128</v>
       </c>
       <c r="BR44" t="s">
-        <v>1053</v>
+        <v>995</v>
       </c>
       <c r="BS44" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="BT44" t="s">
-        <v>1054</v>
+        <v>996</v>
       </c>
       <c r="BU44" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="BV44" t="s">
         <v>136</v>
@@ -15974,40 +15974,40 @@
         <v>138</v>
       </c>
       <c r="BY44" t="s">
-        <v>1055</v>
+        <v>997</v>
       </c>
       <c r="BZ44" t="s">
-        <v>1056</v>
+        <v>998</v>
       </c>
       <c r="CA44" t="s">
         <v>102</v>
       </c>
       <c r="CB44" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="CC44" t="s">
         <v>102</v>
       </c>
       <c r="CD44" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="CE44" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="CF44" t="s">
-        <v>227</v>
+        <v>140</v>
       </c>
       <c r="CG44" t="s">
-        <v>1057</v>
+        <v>999</v>
       </c>
       <c r="CH44" t="s">
-        <v>142</v>
+        <v>257</v>
       </c>
       <c r="CJ44" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="45" spans="1:88">
+    <row r="45" spans="1:88" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>88</v>
       </c>
@@ -16015,7 +16015,7 @@
         <v>46162</v>
       </c>
       <c r="C45" t="s">
-        <v>347</v>
+        <v>145</v>
       </c>
       <c r="D45" t="s">
         <v>90</v>
@@ -16024,16 +16024,16 @@
         <v>91</v>
       </c>
       <c r="F45" t="s">
-        <v>1058</v>
+        <v>1000</v>
       </c>
       <c r="G45" t="s">
-        <v>1059</v>
+        <v>1001</v>
       </c>
       <c r="H45" t="s">
         <v>94</v>
       </c>
       <c r="I45" s="1">
-        <v>37252</v>
+        <v>38586</v>
       </c>
       <c r="J45" t="s">
         <v>95</v>
@@ -16042,31 +16042,31 @@
         <v>96</v>
       </c>
       <c r="L45" t="s">
-        <v>260</v>
+        <v>106</v>
       </c>
       <c r="M45" t="s">
-        <v>106</v>
+        <v>1002</v>
       </c>
       <c r="N45" t="s">
-        <v>1060</v>
+        <v>206</v>
       </c>
       <c r="O45" t="s">
-        <v>207</v>
+        <v>150</v>
       </c>
       <c r="P45" t="s">
-        <v>262</v>
+        <v>101</v>
       </c>
       <c r="Q45" t="s">
         <v>102</v>
       </c>
       <c r="R45" t="s">
-        <v>399</v>
+        <v>152</v>
       </c>
       <c r="S45" t="s">
-        <v>104</v>
+        <v>236</v>
       </c>
       <c r="T45" s="2">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="U45" t="s">
         <v>105</v>
@@ -16078,31 +16078,31 @@
         <v>106</v>
       </c>
       <c r="X45" t="s">
-        <v>209</v>
+        <v>107</v>
       </c>
       <c r="Y45" t="s">
         <v>107</v>
       </c>
       <c r="Z45" t="s">
-        <v>184</v>
+        <v>107</v>
       </c>
       <c r="AA45" t="s">
-        <v>108</v>
+        <v>263</v>
       </c>
       <c r="AB45" t="s">
-        <v>1061</v>
+        <v>106</v>
       </c>
       <c r="AC45" t="s">
         <v>154</v>
       </c>
       <c r="AD45" t="s">
-        <v>154</v>
+        <v>111</v>
       </c>
       <c r="AE45" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AF45" t="s">
-        <v>154</v>
+        <v>111</v>
       </c>
       <c r="AG45" t="s">
         <v>110</v>
@@ -16114,25 +16114,25 @@
         <v>106</v>
       </c>
       <c r="AJ45" t="s">
-        <v>1062</v>
+        <v>1003</v>
       </c>
       <c r="AK45" t="s">
-        <v>239</v>
+        <v>187</v>
       </c>
       <c r="AL45" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="AM45" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="AN45" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="AO45" t="s">
-        <v>265</v>
+        <v>157</v>
       </c>
       <c r="AP45" t="s">
-        <v>212</v>
+        <v>158</v>
       </c>
       <c r="AQ45" t="s">
         <v>159</v>
@@ -16141,34 +16141,34 @@
         <v>106</v>
       </c>
       <c r="AS45" t="s">
-        <v>1042</v>
+        <v>106</v>
       </c>
       <c r="AT45" t="s">
-        <v>1063</v>
+        <v>106</v>
       </c>
       <c r="AU45" t="s">
-        <v>1064</v>
+        <v>1004</v>
       </c>
       <c r="AV45" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="AW45" t="s">
-        <v>1065</v>
+        <v>1005</v>
       </c>
       <c r="AX45" t="s">
-        <v>1066</v>
+        <v>1006</v>
       </c>
       <c r="AY45" t="s">
-        <v>1067</v>
+        <v>1007</v>
       </c>
       <c r="AZ45" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="BA45" t="s">
         <v>114</v>
       </c>
       <c r="BB45" t="s">
-        <v>246</v>
+        <v>114</v>
       </c>
       <c r="BC45" t="s">
         <v>114</v>
@@ -16183,46 +16183,46 @@
         <v>125</v>
       </c>
       <c r="BG45" t="s">
-        <v>1068</v>
+        <v>1008</v>
       </c>
       <c r="BH45" t="s">
-        <v>1069</v>
+        <v>1009</v>
       </c>
       <c r="BI45" t="s">
-        <v>167</v>
+        <v>128</v>
       </c>
       <c r="BJ45" t="s">
-        <v>1070</v>
+        <v>1010</v>
       </c>
       <c r="BK45" t="s">
         <v>128</v>
       </c>
       <c r="BL45" t="s">
-        <v>1071</v>
+        <v>1011</v>
       </c>
       <c r="BM45" t="s">
         <v>128</v>
       </c>
       <c r="BN45" t="s">
-        <v>1072</v>
+        <v>1012</v>
       </c>
       <c r="BO45" t="s">
         <v>130</v>
       </c>
       <c r="BP45" t="s">
-        <v>1073</v>
+        <v>1013</v>
       </c>
       <c r="BQ45" t="s">
         <v>128</v>
       </c>
       <c r="BR45" t="s">
-        <v>1074</v>
+        <v>1014</v>
       </c>
       <c r="BS45" t="s">
-        <v>128</v>
+        <v>167</v>
       </c>
       <c r="BT45" t="s">
-        <v>1075</v>
+        <v>1015</v>
       </c>
       <c r="BU45" t="s">
         <v>128</v>
@@ -16237,13 +16237,13 @@
         <v>138</v>
       </c>
       <c r="BY45" t="s">
-        <v>1076</v>
+        <v>1016</v>
       </c>
       <c r="BZ45" t="s">
-        <v>1077</v>
+        <v>1017</v>
       </c>
       <c r="CA45" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="CB45" t="s">
         <v>102</v>
@@ -16252,16 +16252,16 @@
         <v>102</v>
       </c>
       <c r="CD45" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="CE45" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="CF45" t="s">
-        <v>227</v>
+        <v>140</v>
       </c>
       <c r="CG45" t="s">
-        <v>1078</v>
+        <v>1018</v>
       </c>
       <c r="CH45" t="s">
         <v>142</v>
@@ -16270,15 +16270,15 @@
         <v>177</v>
       </c>
     </row>
-    <row r="46" spans="1:88">
+    <row r="46" spans="1:88" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>88</v>
       </c>
       <c r="B46" s="1">
-        <v>46160</v>
+        <v>46162</v>
       </c>
       <c r="C46" t="s">
-        <v>280</v>
+        <v>145</v>
       </c>
       <c r="D46" t="s">
         <v>90</v>
@@ -16287,16 +16287,16 @@
         <v>91</v>
       </c>
       <c r="F46" t="s">
-        <v>1079</v>
+        <v>1019</v>
       </c>
       <c r="G46" t="s">
-        <v>1080</v>
+        <v>1020</v>
       </c>
       <c r="H46" t="s">
         <v>94</v>
       </c>
       <c r="I46" s="1">
-        <v>35098</v>
+        <v>37292</v>
       </c>
       <c r="J46" t="s">
         <v>95</v>
@@ -16305,16 +16305,16 @@
         <v>96</v>
       </c>
       <c r="L46" t="s">
-        <v>305</v>
+        <v>148</v>
       </c>
       <c r="M46" t="s">
         <v>106</v>
       </c>
       <c r="N46" t="s">
-        <v>1081</v>
+        <v>1021</v>
       </c>
       <c r="O46" t="s">
-        <v>207</v>
+        <v>593</v>
       </c>
       <c r="P46" t="s">
         <v>101</v>
@@ -16326,13 +16326,13 @@
         <v>152</v>
       </c>
       <c r="S46" t="s">
-        <v>236</v>
+        <v>208</v>
       </c>
       <c r="T46" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U46" t="s">
-        <v>307</v>
+        <v>105</v>
       </c>
       <c r="V46" t="s">
         <v>106</v>
@@ -16341,31 +16341,31 @@
         <v>106</v>
       </c>
       <c r="X46" t="s">
-        <v>184</v>
+        <v>107</v>
       </c>
       <c r="Y46" t="s">
-        <v>184</v>
+        <v>107</v>
       </c>
       <c r="Z46" t="s">
         <v>209</v>
       </c>
       <c r="AA46" t="s">
-        <v>263</v>
+        <v>108</v>
       </c>
       <c r="AB46" t="s">
-        <v>106</v>
+        <v>1022</v>
       </c>
       <c r="AC46" t="s">
         <v>111</v>
       </c>
       <c r="AD46" t="s">
-        <v>111</v>
+        <v>154</v>
       </c>
       <c r="AE46" t="s">
-        <v>111</v>
+        <v>154</v>
       </c>
       <c r="AF46" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="AG46" t="s">
         <v>110</v>
@@ -16377,16 +16377,16 @@
         <v>106</v>
       </c>
       <c r="AJ46" t="s">
-        <v>1082</v>
+        <v>1023</v>
       </c>
       <c r="AK46" t="s">
-        <v>239</v>
+        <v>113</v>
       </c>
       <c r="AL46" t="s">
         <v>114</v>
       </c>
       <c r="AM46" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="AN46" t="s">
         <v>114</v>
@@ -16398,10 +16398,10 @@
         <v>116</v>
       </c>
       <c r="AQ46" t="s">
-        <v>114</v>
+        <v>159</v>
       </c>
       <c r="AR46" t="s">
-        <v>1083</v>
+        <v>106</v>
       </c>
       <c r="AS46" t="s">
         <v>118</v>
@@ -16410,19 +16410,19 @@
         <v>106</v>
       </c>
       <c r="AU46" t="s">
-        <v>1084</v>
+        <v>1024</v>
       </c>
       <c r="AV46" t="s">
-        <v>1085</v>
+        <v>164</v>
       </c>
       <c r="AW46" t="s">
-        <v>1086</v>
+        <v>1025</v>
       </c>
       <c r="AX46" t="s">
-        <v>1087</v>
+        <v>1026</v>
       </c>
       <c r="AY46" t="s">
-        <v>1088</v>
+        <v>1027</v>
       </c>
       <c r="AZ46" t="s">
         <v>164</v>
@@ -16434,7 +16434,7 @@
         <v>114</v>
       </c>
       <c r="BC46" t="s">
-        <v>246</v>
+        <v>114</v>
       </c>
       <c r="BD46" t="s">
         <v>102</v>
@@ -16446,46 +16446,46 @@
         <v>125</v>
       </c>
       <c r="BG46" t="s">
-        <v>1089</v>
+        <v>1028</v>
       </c>
       <c r="BH46" t="s">
-        <v>1090</v>
+        <v>1029</v>
       </c>
       <c r="BI46" t="s">
         <v>128</v>
       </c>
       <c r="BJ46" t="s">
-        <v>1091</v>
+        <v>1030</v>
       </c>
       <c r="BK46" t="s">
         <v>128</v>
       </c>
       <c r="BL46" t="s">
-        <v>1092</v>
+        <v>1031</v>
       </c>
       <c r="BM46" t="s">
         <v>128</v>
       </c>
       <c r="BN46" t="s">
-        <v>1093</v>
+        <v>1032</v>
       </c>
       <c r="BO46" t="s">
         <v>128</v>
       </c>
       <c r="BP46" t="s">
-        <v>1094</v>
+        <v>1033</v>
       </c>
       <c r="BQ46" t="s">
         <v>128</v>
       </c>
       <c r="BR46" t="s">
-        <v>1095</v>
+        <v>1034</v>
       </c>
       <c r="BS46" t="s">
         <v>128</v>
       </c>
       <c r="BT46" t="s">
-        <v>1096</v>
+        <v>1035</v>
       </c>
       <c r="BU46" t="s">
         <v>128</v>
@@ -16500,10 +16500,10 @@
         <v>138</v>
       </c>
       <c r="BY46" t="s">
-        <v>1097</v>
+        <v>1036</v>
       </c>
       <c r="BZ46" t="s">
-        <v>1098</v>
+        <v>1037</v>
       </c>
       <c r="CA46" t="s">
         <v>114</v>
@@ -16524,24 +16524,24 @@
         <v>140</v>
       </c>
       <c r="CG46" t="s">
-        <v>1099</v>
+        <v>1038</v>
       </c>
       <c r="CH46" t="s">
-        <v>257</v>
+        <v>142</v>
       </c>
       <c r="CJ46" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="47" spans="1:88">
+    <row r="47" spans="1:88" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>88</v>
       </c>
       <c r="B47" s="1">
-        <v>46160</v>
+        <v>46163</v>
       </c>
       <c r="C47" t="s">
-        <v>653</v>
+        <v>145</v>
       </c>
       <c r="D47" t="s">
         <v>90</v>
@@ -16550,31 +16550,31 @@
         <v>91</v>
       </c>
       <c r="F47" t="s">
-        <v>1100</v>
+        <v>1039</v>
       </c>
       <c r="G47" t="s">
-        <v>1101</v>
+        <v>1040</v>
       </c>
       <c r="H47" t="s">
         <v>94</v>
       </c>
       <c r="I47" s="1">
-        <v>33408</v>
+        <v>38355</v>
       </c>
       <c r="J47" t="s">
-        <v>232</v>
+        <v>95</v>
       </c>
       <c r="K47" t="s">
         <v>96</v>
       </c>
       <c r="L47" t="s">
-        <v>397</v>
+        <v>444</v>
       </c>
       <c r="M47" t="s">
         <v>106</v>
       </c>
       <c r="N47" t="s">
-        <v>1102</v>
+        <v>1041</v>
       </c>
       <c r="O47" t="s">
         <v>182</v>
@@ -16586,13 +16586,13 @@
         <v>102</v>
       </c>
       <c r="R47" t="s">
-        <v>183</v>
+        <v>152</v>
       </c>
       <c r="S47" t="s">
-        <v>236</v>
+        <v>208</v>
       </c>
       <c r="T47" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U47" t="s">
         <v>105</v>
@@ -16607,28 +16607,28 @@
         <v>209</v>
       </c>
       <c r="Y47" t="s">
-        <v>184</v>
+        <v>107</v>
       </c>
       <c r="Z47" t="s">
         <v>107</v>
       </c>
       <c r="AA47" t="s">
-        <v>447</v>
+        <v>263</v>
       </c>
       <c r="AB47" t="s">
-        <v>1103</v>
+        <v>106</v>
       </c>
       <c r="AC47" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AD47" t="s">
         <v>111</v>
       </c>
       <c r="AE47" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AF47" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AG47" t="s">
         <v>110</v>
@@ -16640,13 +16640,13 @@
         <v>106</v>
       </c>
       <c r="AJ47" t="s">
-        <v>211</v>
+        <v>553</v>
       </c>
       <c r="AK47" t="s">
-        <v>239</v>
+        <v>156</v>
       </c>
       <c r="AL47" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="AM47" t="s">
         <v>114</v>
@@ -16655,40 +16655,40 @@
         <v>114</v>
       </c>
       <c r="AO47" t="s">
-        <v>157</v>
+        <v>115</v>
       </c>
       <c r="AP47" t="s">
-        <v>212</v>
+        <v>158</v>
       </c>
       <c r="AQ47" t="s">
-        <v>114</v>
+        <v>159</v>
       </c>
       <c r="AR47" t="s">
-        <v>1104</v>
+        <v>106</v>
       </c>
       <c r="AS47" t="s">
-        <v>118</v>
+        <v>1042</v>
       </c>
       <c r="AT47" t="s">
         <v>106</v>
       </c>
       <c r="AU47" t="s">
-        <v>1105</v>
+        <v>1043</v>
       </c>
       <c r="AV47" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="AW47" t="s">
-        <v>1106</v>
+        <v>1044</v>
       </c>
       <c r="AX47" t="s">
-        <v>1107</v>
+        <v>1045</v>
       </c>
       <c r="AY47" t="s">
-        <v>1108</v>
+        <v>1046</v>
       </c>
       <c r="AZ47" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="BA47" t="s">
         <v>114</v>
@@ -16697,7 +16697,7 @@
         <v>114</v>
       </c>
       <c r="BC47" t="s">
-        <v>114</v>
+        <v>246</v>
       </c>
       <c r="BD47" t="s">
         <v>102</v>
@@ -16709,70 +16709,70 @@
         <v>125</v>
       </c>
       <c r="BG47" t="s">
-        <v>1109</v>
+        <v>1047</v>
       </c>
       <c r="BH47" t="s">
-        <v>1110</v>
+        <v>1048</v>
       </c>
       <c r="BI47" t="s">
         <v>128</v>
       </c>
       <c r="BJ47" t="s">
-        <v>1111</v>
+        <v>1049</v>
       </c>
       <c r="BK47" t="s">
-        <v>167</v>
+        <v>128</v>
       </c>
       <c r="BL47" t="s">
-        <v>1112</v>
+        <v>1050</v>
       </c>
       <c r="BM47" t="s">
-        <v>167</v>
+        <v>128</v>
       </c>
       <c r="BN47" t="s">
-        <v>1113</v>
+        <v>1051</v>
       </c>
       <c r="BO47" t="s">
-        <v>167</v>
+        <v>130</v>
       </c>
       <c r="BP47" t="s">
-        <v>1114</v>
+        <v>1052</v>
       </c>
       <c r="BQ47" t="s">
         <v>128</v>
       </c>
       <c r="BR47" t="s">
-        <v>1115</v>
+        <v>1053</v>
       </c>
       <c r="BS47" t="s">
         <v>130</v>
       </c>
       <c r="BT47" t="s">
-        <v>1116</v>
+        <v>1054</v>
       </c>
       <c r="BU47" t="s">
-        <v>167</v>
+        <v>130</v>
       </c>
       <c r="BV47" t="s">
-        <v>200</v>
+        <v>136</v>
       </c>
       <c r="BW47" t="s">
-        <v>200</v>
+        <v>137</v>
       </c>
       <c r="BX47" t="s">
-        <v>777</v>
+        <v>138</v>
       </c>
       <c r="BY47" t="s">
-        <v>1117</v>
+        <v>1055</v>
       </c>
       <c r="BZ47" t="s">
-        <v>1118</v>
+        <v>1056</v>
       </c>
       <c r="CA47" t="s">
         <v>102</v>
       </c>
       <c r="CB47" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="CC47" t="s">
         <v>102</v>
@@ -16781,13 +16781,13 @@
         <v>102</v>
       </c>
       <c r="CE47" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="CF47" t="s">
         <v>227</v>
       </c>
       <c r="CG47" t="s">
-        <v>1119</v>
+        <v>1057</v>
       </c>
       <c r="CH47" t="s">
         <v>142</v>
@@ -16796,15 +16796,15 @@
         <v>177</v>
       </c>
     </row>
-    <row r="48" spans="1:88">
+    <row r="48" spans="1:88" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>88</v>
       </c>
       <c r="B48" s="1">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="C48" t="s">
-        <v>89</v>
+        <v>347</v>
       </c>
       <c r="D48" t="s">
         <v>90</v>
@@ -16813,16 +16813,16 @@
         <v>91</v>
       </c>
       <c r="F48" t="s">
-        <v>1120</v>
+        <v>1058</v>
       </c>
       <c r="G48" t="s">
-        <v>1121</v>
+        <v>1059</v>
       </c>
       <c r="H48" t="s">
         <v>94</v>
       </c>
       <c r="I48" s="1">
-        <v>34880</v>
+        <v>37252</v>
       </c>
       <c r="J48" t="s">
         <v>95</v>
@@ -16831,16 +16831,16 @@
         <v>96</v>
       </c>
       <c r="L48" t="s">
-        <v>305</v>
+        <v>260</v>
       </c>
       <c r="M48" t="s">
         <v>106</v>
       </c>
       <c r="N48" t="s">
-        <v>1122</v>
+        <v>1060</v>
       </c>
       <c r="O48" t="s">
-        <v>182</v>
+        <v>207</v>
       </c>
       <c r="P48" t="s">
         <v>262</v>
@@ -16849,13 +16849,13 @@
         <v>102</v>
       </c>
       <c r="R48" t="s">
-        <v>352</v>
+        <v>399</v>
       </c>
       <c r="S48" t="s">
         <v>104</v>
       </c>
       <c r="T48" s="2">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="U48" t="s">
         <v>105</v>
@@ -16879,19 +16879,19 @@
         <v>108</v>
       </c>
       <c r="AB48" t="s">
-        <v>1123</v>
+        <v>1061</v>
       </c>
       <c r="AC48" t="s">
-        <v>110</v>
+        <v>154</v>
       </c>
       <c r="AD48" t="s">
-        <v>110</v>
+        <v>154</v>
       </c>
       <c r="AE48" t="s">
         <v>110</v>
       </c>
       <c r="AF48" t="s">
-        <v>110</v>
+        <v>154</v>
       </c>
       <c r="AG48" t="s">
         <v>110</v>
@@ -16903,7 +16903,7 @@
         <v>106</v>
       </c>
       <c r="AJ48" t="s">
-        <v>1124</v>
+        <v>1062</v>
       </c>
       <c r="AK48" t="s">
         <v>239</v>
@@ -16915,103 +16915,103 @@
         <v>114</v>
       </c>
       <c r="AN48" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="AO48" t="s">
-        <v>115</v>
+        <v>265</v>
       </c>
       <c r="AP48" t="s">
-        <v>309</v>
+        <v>212</v>
       </c>
       <c r="AQ48" t="s">
-        <v>114</v>
+        <v>159</v>
       </c>
       <c r="AR48" t="s">
-        <v>1125</v>
+        <v>106</v>
       </c>
       <c r="AS48" t="s">
-        <v>118</v>
+        <v>1042</v>
       </c>
       <c r="AT48" t="s">
-        <v>106</v>
+        <v>1063</v>
       </c>
       <c r="AU48" t="s">
-        <v>1126</v>
+        <v>1064</v>
       </c>
       <c r="AV48" t="s">
-        <v>106</v>
+        <v>120</v>
       </c>
       <c r="AW48" t="s">
-        <v>1127</v>
+        <v>1065</v>
       </c>
       <c r="AX48" t="s">
-        <v>1128</v>
+        <v>1066</v>
       </c>
       <c r="AY48" t="s">
-        <v>1129</v>
+        <v>1067</v>
       </c>
       <c r="AZ48" t="s">
-        <v>1130</v>
+        <v>120</v>
       </c>
       <c r="BA48" t="s">
         <v>114</v>
       </c>
       <c r="BB48" t="s">
-        <v>114</v>
+        <v>246</v>
       </c>
       <c r="BC48" t="s">
         <v>114</v>
       </c>
       <c r="BD48" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="BE48" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="BF48" t="s">
         <v>125</v>
       </c>
       <c r="BG48" t="s">
-        <v>106</v>
+        <v>1068</v>
       </c>
       <c r="BH48" t="s">
-        <v>1131</v>
+        <v>1069</v>
       </c>
       <c r="BI48" t="s">
-        <v>128</v>
+        <v>167</v>
       </c>
       <c r="BJ48" t="s">
-        <v>1132</v>
+        <v>1070</v>
       </c>
       <c r="BK48" t="s">
         <v>128</v>
       </c>
       <c r="BL48" t="s">
-        <v>1133</v>
+        <v>1071</v>
       </c>
       <c r="BM48" t="s">
         <v>128</v>
       </c>
       <c r="BN48" t="s">
-        <v>1134</v>
+        <v>1072</v>
       </c>
       <c r="BO48" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="BP48" t="s">
-        <v>1135</v>
+        <v>1073</v>
       </c>
       <c r="BQ48" t="s">
         <v>128</v>
       </c>
       <c r="BR48" t="s">
-        <v>1136</v>
+        <v>1074</v>
       </c>
       <c r="BS48" t="s">
         <v>128</v>
       </c>
       <c r="BT48" t="s">
-        <v>1137</v>
+        <v>1075</v>
       </c>
       <c r="BU48" t="s">
         <v>128</v>
@@ -17026,16 +17026,16 @@
         <v>138</v>
       </c>
       <c r="BY48" t="s">
-        <v>106</v>
+        <v>1076</v>
       </c>
       <c r="BZ48" t="s">
-        <v>1138</v>
+        <v>1077</v>
       </c>
       <c r="CA48" t="s">
         <v>102</v>
       </c>
       <c r="CB48" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="CC48" t="s">
         <v>102</v>
@@ -17044,22 +17044,22 @@
         <v>102</v>
       </c>
       <c r="CE48" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="CF48" t="s">
         <v>227</v>
       </c>
       <c r="CG48" t="s">
-        <v>106</v>
+        <v>1078</v>
       </c>
       <c r="CH48" t="s">
-        <v>257</v>
+        <v>142</v>
       </c>
       <c r="CJ48" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="49" spans="1:90">
+    <row r="49" spans="1:90" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>88</v>
       </c>
@@ -17328,7 +17328,7 @@
         <v>1161</v>
       </c>
     </row>
-    <row r="50" spans="1:90">
+    <row r="50" spans="1:90" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>88</v>
       </c>
@@ -17597,7 +17597,7 @@
         <v>1161</v>
       </c>
     </row>
-    <row r="51" spans="1:90">
+    <row r="51" spans="1:90" x14ac:dyDescent="0.25">
       <c r="B51" s="1"/>
       <c r="E51" s="3" t="s">
         <v>91</v>
@@ -17855,19 +17855,22 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="54c5ab46-7543-4aba-b0fa-79d6a199bef5" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="20d57abc-823c-4051-a81a-1a0a01a8f39e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -18106,24 +18109,33 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="54c5ab46-7543-4aba-b0fa-79d6a199bef5" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="20d57abc-823c-4051-a81a-1a0a01a8f39e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E5422FBB-6025-4E11-8C1C-C4A520C0A5F3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F6C6D4B0-20F6-407F-B938-614BBBC09F61}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="54c5ab46-7543-4aba-b0fa-79d6a199bef5"/>
+    <ds:schemaRef ds:uri="20d57abc-823c-4051-a81a-1a0a01a8f39e"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{58C53962-3743-4746-B884-C17F9FB7D8EC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9C5639F8-A3F7-4745-96CC-DA79E96C1DD3}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F6C6D4B0-20F6-407F-B938-614BBBC09F61}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E5422FBB-6025-4E11-8C1C-C4A520C0A5F3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>